--- a/research/traditional_assets/database/data/philippines/philippines_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_green_renewable_energy.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_aslag" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,83 +589,116 @@
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
+      <c r="G2">
+        <v>0.6298456260720411</v>
+      </c>
+      <c r="H2">
+        <v>0.6298456260720411</v>
+      </c>
+      <c r="I2">
+        <v>0.2490566037735849</v>
+      </c>
+      <c r="J2">
+        <v>0.2490566037735849</v>
+      </c>
       <c r="K2">
-        <v>-0.482</v>
+        <v>0.6320000000000001</v>
+      </c>
+      <c r="L2">
+        <v>0.1084048027444254</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.005764796310530362</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>2.373417721518987</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.005764796310530362</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>2.373417721518987</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.007</v>
+        <v>43.7</v>
       </c>
       <c r="V2">
-        <v>3.465346534653466e-05</v>
+        <v>0.1679477325134512</v>
+      </c>
+      <c r="W2">
+        <v>-0.01782592592592592</v>
       </c>
       <c r="X2">
-        <v>0.0607705476502472</v>
+        <v>0.1196186381571616</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1374445640830875</v>
+      </c>
+      <c r="Z2">
+        <v>0.1025289296894235</v>
+      </c>
+      <c r="AA2">
+        <v>0.002513102528982441</v>
       </c>
       <c r="AB2">
-        <v>0.05992038437439384</v>
+        <v>0.1081300761685645</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1056169736395821</v>
       </c>
       <c r="AD2">
-        <v>6.39</v>
+        <v>25.97</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.39</v>
+        <v>25.97</v>
       </c>
       <c r="AG2">
-        <v>6.383</v>
+        <v>-17.73</v>
       </c>
       <c r="AH2">
-        <v>0.03066365948462018</v>
+        <v>0.09075025334591327</v>
       </c>
       <c r="AI2">
-        <v>0.3761035903472631</v>
+        <v>0.1603383342594308</v>
       </c>
       <c r="AJ2">
-        <v>0.03063109754634495</v>
+        <v>-0.07312244813791399</v>
       </c>
       <c r="AK2">
-        <v>0.3758464346699641</v>
+        <v>-0.1499112200896255</v>
       </c>
       <c r="AL2">
-        <v>0.156</v>
+        <v>0.9309999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.156</v>
+        <v>0.858</v>
       </c>
       <c r="AN2">
-        <v>-38.96341463414634</v>
+        <v>8.688524590163935</v>
       </c>
       <c r="AO2">
-        <v>-1.583333333333333</v>
+        <v>1.559613319011815</v>
       </c>
       <c r="AP2">
-        <v>-38.92073170731707</v>
+        <v>-5.931749749079962</v>
       </c>
       <c r="AQ2">
-        <v>-1.583333333333333</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solar Philippines Nueva Ecija Corporation (PSE:SPNEC)</t>
+          <t>Raslag Corporation (PSE:ASLAG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -682,83 +717,8938 @@
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.758147512864494</v>
+      </c>
+      <c r="H3">
+        <v>0.758147512864494</v>
+      </c>
+      <c r="I3">
+        <v>0.3893653516295026</v>
+      </c>
+      <c r="J3">
+        <v>0.3893653516295026</v>
+      </c>
       <c r="K3">
-        <v>-0.482</v>
+        <v>1.57</v>
+      </c>
+      <c r="L3">
+        <v>0.2692967409948542</v>
       </c>
       <c r="M3">
+        <v>1.5</v>
+      </c>
+      <c r="N3">
+        <v>0.03355704697986577</v>
+      </c>
+      <c r="O3">
+        <v>0.9554140127388535</v>
+      </c>
+      <c r="P3">
+        <v>1.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.03355704697986577</v>
+      </c>
+      <c r="R3">
+        <v>0.9554140127388535</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>11.5</v>
+      </c>
+      <c r="V3">
+        <v>0.2572706935123042</v>
+      </c>
+      <c r="W3">
+        <v>0.05814814814814815</v>
+      </c>
+      <c r="X3">
+        <v>0.1307315614271389</v>
+      </c>
+      <c r="Y3">
+        <v>-0.07258341327899079</v>
+      </c>
+      <c r="Z3">
+        <v>0.1431377363123005</v>
+      </c>
+      <c r="AA3">
+        <v>0.0557328750306899</v>
+      </c>
+      <c r="AB3">
+        <v>0.108986793351642</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05325391832095206</v>
+      </c>
+      <c r="AD3">
+        <v>20.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>20.5</v>
+      </c>
+      <c r="AG3">
+        <v>9</v>
+      </c>
+      <c r="AH3">
+        <v>0.3144171779141104</v>
+      </c>
+      <c r="AI3">
+        <v>0.3596491228070176</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1675977653631285</v>
+      </c>
+      <c r="AK3">
+        <v>0.1978021978021978</v>
+      </c>
+      <c r="AL3">
+        <v>0.853</v>
+      </c>
+      <c r="AM3">
+        <v>0.79</v>
+      </c>
+      <c r="AN3">
+        <v>5.452127659574469</v>
+      </c>
+      <c r="AO3">
+        <v>2.661195779601407</v>
+      </c>
+      <c r="AP3">
+        <v>2.393617021276596</v>
+      </c>
+      <c r="AQ3">
+        <v>2.873417721518987</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SP New Energy Corporation (PSE:SPNEC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Green &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-0.9379999999999999</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>32.2</v>
+      </c>
+      <c r="V4">
+        <v>0.1494199535962877</v>
+      </c>
+      <c r="W4">
+        <v>-0.09379999999999999</v>
+      </c>
+      <c r="X4">
+        <v>0.1085057148871843</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2023057148871842</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05070666997272502</v>
+      </c>
+      <c r="AB4">
+        <v>0.107273358985487</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1579800289582121</v>
+      </c>
+      <c r="AD4">
+        <v>5.47</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>5.47</v>
+      </c>
+      <c r="AG4">
+        <v>-26.73</v>
+      </c>
+      <c r="AH4">
+        <v>0.02475449155994026</v>
+      </c>
+      <c r="AI4">
+        <v>0.05211012670286749</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1416008899719235</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3673216985021301</v>
+      </c>
+      <c r="AL4">
+        <v>0.078</v>
+      </c>
+      <c r="AM4">
+        <v>0.068</v>
+      </c>
+      <c r="AN4">
+        <v>-7.094682230869001</v>
+      </c>
+      <c r="AO4">
+        <v>-10.48717948717949</v>
+      </c>
+      <c r="AP4">
+        <v>34.66926070038911</v>
+      </c>
+      <c r="AQ4">
+        <v>-12.02941176470588</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raslag Corporation (PSE:ASLAG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:ASLAG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Green &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.31441717791411</v>
+      </c>
+      <c r="F2">
+        <v>0.23</v>
+      </c>
+      <c r="G2">
+        <v>44.7</v>
+      </c>
+      <c r="H2">
+        <v>54.4589463592152</v>
+      </c>
+      <c r="I2">
+        <v>53.7</v>
+      </c>
+      <c r="J2">
+        <v>57.9549463592152</v>
+      </c>
+      <c r="K2">
+        <v>20.5</v>
+      </c>
+      <c r="L2">
+        <v>14.996</v>
+      </c>
+      <c r="M2">
+        <v>0.108986793351642</v>
+      </c>
+      <c r="N2">
+        <v>0.103833807116688</v>
+      </c>
+      <c r="O2">
+        <v>0.0615725917431193</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.130731561427139</v>
+      </c>
+      <c r="T2">
+        <v>0.122527671580114</v>
+      </c>
+      <c r="U2">
+        <v>0.9991971635008</v>
+      </c>
+      <c r="V2">
+        <v>0.910029707432762</v>
+      </c>
+      <c r="W2">
+        <v>4.51635587671864</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>44.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.08209678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.76</v>
+      </c>
+      <c r="AH2">
+        <v>0.035</v>
+      </c>
+      <c r="AI2">
+        <v>11.1</v>
+      </c>
+      <c r="AJ2">
+        <v>20.5</v>
+      </c>
+      <c r="AK2">
+        <v>20.5</v>
+      </c>
+      <c r="AL2">
+        <v>0.853</v>
+      </c>
+      <c r="AM2">
+        <v>20.5</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1072035088771221</v>
+      </c>
+      <c r="C2">
+        <v>66.59996292374038</v>
+      </c>
+      <c r="D2">
+        <v>55.09996292374038</v>
+      </c>
+      <c r="E2">
+        <v>-20.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>11.5</v>
+      </c>
+      <c r="H2">
+        <v>44.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.76</v>
+      </c>
+      <c r="K2">
+        <v>0.035</v>
+      </c>
+      <c r="L2">
+        <v>3.725</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>3.725</v>
+      </c>
+      <c r="O2">
+        <v>0.9312499999999999</v>
+      </c>
+      <c r="P2">
+        <v>2.79375</v>
+      </c>
+      <c r="Q2">
+        <v>2.82875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1072035088771221</v>
+      </c>
+      <c r="T2">
+        <v>0.7434725461254394</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1069872501049293</v>
+      </c>
+      <c r="C3">
+        <v>66.12271480640788</v>
+      </c>
+      <c r="D3">
+        <v>55.27471480640789</v>
+      </c>
+      <c r="E3">
+        <v>-19.848</v>
+      </c>
+      <c r="F3">
+        <v>0.652</v>
+      </c>
+      <c r="G3">
+        <v>11.5</v>
+      </c>
+      <c r="H3">
+        <v>44.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.76</v>
+      </c>
+      <c r="K3">
+        <v>0.035</v>
+      </c>
+      <c r="L3">
+        <v>3.725</v>
+      </c>
+      <c r="M3">
+        <v>0.0297964</v>
+      </c>
       <c r="N3">
-        <v>-0</v>
+        <v>3.6952036</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.9238008999999999</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.7714027</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>2.8064027</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1077217172777064</v>
+      </c>
+      <c r="T3">
+        <v>0.749104913899117</v>
       </c>
       <c r="U3">
-        <v>0.007</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>3.465346534653466e-05</v>
-      </c>
-      <c r="X3">
-        <v>0.0607705476502472</v>
-      </c>
-      <c r="AB3">
-        <v>0.05992038437439384</v>
-      </c>
-      <c r="AD3">
-        <v>6.39</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>6.39</v>
-      </c>
-      <c r="AG3">
-        <v>6.383</v>
-      </c>
-      <c r="AH3">
-        <v>0.03066365948462018</v>
-      </c>
-      <c r="AI3">
-        <v>0.3761035903472631</v>
-      </c>
-      <c r="AJ3">
-        <v>0.03063109754634495</v>
-      </c>
-      <c r="AK3">
-        <v>0.3758464346699641</v>
-      </c>
-      <c r="AL3">
-        <v>0.156</v>
-      </c>
-      <c r="AM3">
-        <v>0.156</v>
-      </c>
-      <c r="AN3">
-        <v>-38.96341463414634</v>
-      </c>
-      <c r="AO3">
-        <v>-1.583333333333333</v>
-      </c>
-      <c r="AP3">
-        <v>-38.92073170731707</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.583333333333333</v>
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>125.0151024956035</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1067709913327365</v>
+      </c>
+      <c r="C4">
+        <v>65.64657868190773</v>
+      </c>
+      <c r="D4">
+        <v>55.45057868190773</v>
+      </c>
+      <c r="E4">
+        <v>-19.196</v>
+      </c>
+      <c r="F4">
+        <v>1.304</v>
+      </c>
+      <c r="G4">
+        <v>11.5</v>
+      </c>
+      <c r="H4">
+        <v>44.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.76</v>
+      </c>
+      <c r="K4">
+        <v>0.035</v>
+      </c>
+      <c r="L4">
+        <v>3.725</v>
+      </c>
+      <c r="M4">
+        <v>0.05959280000000001</v>
+      </c>
+      <c r="N4">
+        <v>3.6654072</v>
+      </c>
+      <c r="O4">
+        <v>0.9163517999999999</v>
+      </c>
+      <c r="P4">
+        <v>2.7490554</v>
+      </c>
+      <c r="Q4">
+        <v>2.7840554</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1082505013599352</v>
+      </c>
+      <c r="T4">
+        <v>0.7548522279538901</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>62.50755124780174</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1065547325605437</v>
+      </c>
+      <c r="C5">
+        <v>65.17156519797753</v>
+      </c>
+      <c r="D5">
+        <v>55.62756519797752</v>
+      </c>
+      <c r="E5">
+        <v>-18.544</v>
+      </c>
+      <c r="F5">
+        <v>1.956</v>
+      </c>
+      <c r="G5">
+        <v>11.5</v>
+      </c>
+      <c r="H5">
+        <v>44.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.76</v>
+      </c>
+      <c r="K5">
+        <v>0.035</v>
+      </c>
+      <c r="L5">
+        <v>3.725</v>
+      </c>
+      <c r="M5">
+        <v>0.0893892</v>
+      </c>
+      <c r="N5">
+        <v>3.6356108</v>
+      </c>
+      <c r="O5">
+        <v>0.9089027</v>
+      </c>
+      <c r="P5">
+        <v>2.7267081</v>
+      </c>
+      <c r="Q5">
+        <v>2.7617081</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1087901882067461</v>
+      </c>
+      <c r="T5">
+        <v>0.76071804332938</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>41.67170083186783</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1063384737883509</v>
+      </c>
+      <c r="C6">
+        <v>64.69768513873142</v>
+      </c>
+      <c r="D6">
+        <v>55.80568513873142</v>
+      </c>
+      <c r="E6">
+        <v>-17.892</v>
+      </c>
+      <c r="F6">
+        <v>2.608</v>
+      </c>
+      <c r="G6">
+        <v>11.5</v>
+      </c>
+      <c r="H6">
+        <v>44.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.76</v>
+      </c>
+      <c r="K6">
+        <v>0.035</v>
+      </c>
+      <c r="L6">
+        <v>3.725</v>
+      </c>
+      <c r="M6">
+        <v>0.1191856</v>
+      </c>
+      <c r="N6">
+        <v>3.605814399999999</v>
+      </c>
+      <c r="O6">
+        <v>0.9014535999999999</v>
+      </c>
+      <c r="P6">
+        <v>2.704360799999999</v>
+      </c>
+      <c r="Q6">
+        <v>2.7393608</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1093411185295322</v>
+      </c>
+      <c r="T6">
+        <v>0.7667060631918594</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>31.25377562390086</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1061222150161581</v>
+      </c>
+      <c r="C7">
+        <v>64.22494942685063</v>
+      </c>
+      <c r="D7">
+        <v>55.98494942685063</v>
+      </c>
+      <c r="E7">
+        <v>-17.24</v>
+      </c>
+      <c r="F7">
+        <v>3.26</v>
+      </c>
+      <c r="G7">
+        <v>11.5</v>
+      </c>
+      <c r="H7">
+        <v>44.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.76</v>
+      </c>
+      <c r="K7">
+        <v>0.035</v>
+      </c>
+      <c r="L7">
+        <v>3.725</v>
+      </c>
+      <c r="M7">
+        <v>0.148982</v>
+      </c>
+      <c r="N7">
+        <v>3.576017999999999</v>
+      </c>
+      <c r="O7">
+        <v>0.8940044999999999</v>
+      </c>
+      <c r="P7">
+        <v>2.6820135</v>
+      </c>
+      <c r="Q7">
+        <v>2.7170135</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1099036473854296</v>
+      </c>
+      <c r="T7">
+        <v>0.772820146630391</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>25.00302049912069</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1059059562439653</v>
+      </c>
+      <c r="C8">
+        <v>63.75336912581611</v>
+      </c>
+      <c r="D8">
+        <v>56.16536912581611</v>
+      </c>
+      <c r="E8">
+        <v>-16.588</v>
+      </c>
+      <c r="F8">
+        <v>3.912</v>
+      </c>
+      <c r="G8">
+        <v>11.5</v>
+      </c>
+      <c r="H8">
+        <v>44.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.76</v>
+      </c>
+      <c r="K8">
+        <v>0.035</v>
+      </c>
+      <c r="L8">
+        <v>3.725</v>
+      </c>
+      <c r="M8">
+        <v>0.1787784</v>
+      </c>
+      <c r="N8">
+        <v>3.5462216</v>
+      </c>
+      <c r="O8">
+        <v>0.8865553999999999</v>
+      </c>
+      <c r="P8">
+        <v>2.6596662</v>
+      </c>
+      <c r="Q8">
+        <v>2.6946662</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1104781449403886</v>
+      </c>
+      <c r="T8">
+        <v>0.7790643169505934</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>20.83585041593391</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1056896974717725</v>
+      </c>
+      <c r="C9">
+        <v>63.28295544218464</v>
+      </c>
+      <c r="D9">
+        <v>56.34695544218464</v>
+      </c>
+      <c r="E9">
+        <v>-15.936</v>
+      </c>
+      <c r="F9">
+        <v>4.564000000000001</v>
+      </c>
+      <c r="G9">
+        <v>11.5</v>
+      </c>
+      <c r="H9">
+        <v>44.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.76</v>
+      </c>
+      <c r="K9">
+        <v>0.035</v>
+      </c>
+      <c r="L9">
+        <v>3.725</v>
+      </c>
+      <c r="M9">
+        <v>0.2085748000000001</v>
+      </c>
+      <c r="N9">
+        <v>3.5164252</v>
+      </c>
+      <c r="O9">
+        <v>0.8791062999999999</v>
+      </c>
+      <c r="P9">
+        <v>2.637318899999999</v>
+      </c>
+      <c r="Q9">
+        <v>2.6723189</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1110649972814758</v>
+      </c>
+      <c r="T9">
+        <v>0.7854427705034884</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>17.85930035651478</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1054734386995797</v>
+      </c>
+      <c r="C10">
+        <v>62.8137197279092</v>
+      </c>
+      <c r="D10">
+        <v>56.5297197279092</v>
+      </c>
+      <c r="E10">
+        <v>-15.284</v>
+      </c>
+      <c r="F10">
+        <v>5.216</v>
+      </c>
+      <c r="G10">
+        <v>11.5</v>
+      </c>
+      <c r="H10">
+        <v>44.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.76</v>
+      </c>
+      <c r="K10">
+        <v>0.035</v>
+      </c>
+      <c r="L10">
+        <v>3.725</v>
+      </c>
+      <c r="M10">
+        <v>0.2383712</v>
+      </c>
+      <c r="N10">
+        <v>3.4866288</v>
+      </c>
+      <c r="O10">
+        <v>0.8716571999999999</v>
+      </c>
+      <c r="P10">
+        <v>2.6149716</v>
+      </c>
+      <c r="Q10">
+        <v>2.6499716</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1116646072821518</v>
+      </c>
+      <c r="T10">
+        <v>0.7919598860901421</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>15.62688781195043</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1052571799273869</v>
+      </c>
+      <c r="C11">
+        <v>62.34567348270468</v>
+      </c>
+      <c r="D11">
+        <v>56.71367348270468</v>
+      </c>
+      <c r="E11">
+        <v>-14.632</v>
+      </c>
+      <c r="F11">
+        <v>5.868</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <v>44.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.76</v>
+      </c>
+      <c r="K11">
+        <v>0.035</v>
+      </c>
+      <c r="L11">
+        <v>3.725</v>
+      </c>
+      <c r="M11">
+        <v>0.2681676000000001</v>
+      </c>
+      <c r="N11">
+        <v>3.4568324</v>
+      </c>
+      <c r="O11">
+        <v>0.8642080999999999</v>
+      </c>
+      <c r="P11">
+        <v>2.5926243</v>
+      </c>
+      <c r="Q11">
+        <v>2.6276243</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1122773955246009</v>
+      </c>
+      <c r="T11">
+        <v>0.7986202349863923</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.034275</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>13.89056694395594</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.105160921155194</v>
+      </c>
+      <c r="C12">
+        <v>61.77593859417325</v>
+      </c>
+      <c r="D12">
+        <v>56.79593859417325</v>
+      </c>
+      <c r="E12">
+        <v>-13.98</v>
+      </c>
+      <c r="F12">
+        <v>6.52</v>
+      </c>
+      <c r="G12">
+        <v>11.5</v>
+      </c>
+      <c r="H12">
+        <v>44.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.76</v>
+      </c>
+      <c r="K12">
+        <v>0.035</v>
+      </c>
+      <c r="L12">
+        <v>3.725</v>
+      </c>
+      <c r="M12">
+        <v>0.3083960000000001</v>
+      </c>
+      <c r="N12">
+        <v>3.416604</v>
+      </c>
+      <c r="O12">
+        <v>0.8541509999999999</v>
+      </c>
+      <c r="P12">
+        <v>2.562453</v>
+      </c>
+      <c r="Q12">
+        <v>2.597453</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1129038012835489</v>
+      </c>
+      <c r="T12">
+        <v>0.8054285916358926</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.035475</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>12.07862618192194</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1049566623830012</v>
+      </c>
+      <c r="C13">
+        <v>61.299296120761</v>
+      </c>
+      <c r="D13">
+        <v>56.971296120761</v>
+      </c>
+      <c r="E13">
+        <v>-13.328</v>
+      </c>
+      <c r="F13">
+        <v>7.172000000000001</v>
+      </c>
+      <c r="G13">
+        <v>11.5</v>
+      </c>
+      <c r="H13">
+        <v>44.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.76</v>
+      </c>
+      <c r="K13">
+        <v>0.035</v>
+      </c>
+      <c r="L13">
+        <v>3.725</v>
+      </c>
+      <c r="M13">
+        <v>0.3392356</v>
+      </c>
+      <c r="N13">
+        <v>3.3857644</v>
+      </c>
+      <c r="O13">
+        <v>0.8464410999999999</v>
+      </c>
+      <c r="P13">
+        <v>2.5393233</v>
+      </c>
+      <c r="Q13">
+        <v>2.5743233</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1135442835764059</v>
+      </c>
+      <c r="T13">
+        <v>0.8123899450640336</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.035475</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>10.98056925629268</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1050944036108084</v>
+      </c>
+      <c r="C14">
+        <v>60.52892570259554</v>
+      </c>
+      <c r="D14">
+        <v>56.85292570259553</v>
+      </c>
+      <c r="E14">
+        <v>-12.676</v>
+      </c>
+      <c r="F14">
+        <v>7.824</v>
+      </c>
+      <c r="G14">
+        <v>11.5</v>
+      </c>
+      <c r="H14">
+        <v>44.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.76</v>
+      </c>
+      <c r="K14">
+        <v>0.035</v>
+      </c>
+      <c r="L14">
+        <v>3.725</v>
+      </c>
+      <c r="M14">
+        <v>0.3998064</v>
+      </c>
+      <c r="N14">
+        <v>3.3251936</v>
+      </c>
+      <c r="O14">
+        <v>0.8312983999999999</v>
+      </c>
+      <c r="P14">
+        <v>2.4938952</v>
+      </c>
+      <c r="Q14">
+        <v>2.5288952</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1141993222850096</v>
+      </c>
+      <c r="T14">
+        <v>0.8195095110700866</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.038325</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>9.31700943256536</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1049186448386156</v>
+      </c>
+      <c r="C15">
+        <v>60.02805403321162</v>
+      </c>
+      <c r="D15">
+        <v>57.00405403321162</v>
+      </c>
+      <c r="E15">
+        <v>-12.024</v>
+      </c>
+      <c r="F15">
+        <v>8.476000000000001</v>
+      </c>
+      <c r="G15">
+        <v>11.5</v>
+      </c>
+      <c r="H15">
+        <v>44.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.76</v>
+      </c>
+      <c r="K15">
+        <v>0.035</v>
+      </c>
+      <c r="L15">
+        <v>3.725</v>
+      </c>
+      <c r="M15">
+        <v>0.4331236000000001</v>
+      </c>
+      <c r="N15">
+        <v>3.2918764</v>
+      </c>
+      <c r="O15">
+        <v>0.8229690999999999</v>
+      </c>
+      <c r="P15">
+        <v>2.4689073</v>
+      </c>
+      <c r="Q15">
+        <v>2.5039073</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1148694193547306</v>
+      </c>
+      <c r="T15">
+        <v>0.826792745260187</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.038325</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>8.600316399291101</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1047428860664228</v>
+      </c>
+      <c r="C16">
+        <v>59.52798797399785</v>
+      </c>
+      <c r="D16">
+        <v>57.15598797399785</v>
+      </c>
+      <c r="E16">
+        <v>-11.372</v>
+      </c>
+      <c r="F16">
+        <v>9.128000000000002</v>
+      </c>
+      <c r="G16">
+        <v>11.5</v>
+      </c>
+      <c r="H16">
+        <v>44.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.76</v>
+      </c>
+      <c r="K16">
+        <v>0.035</v>
+      </c>
+      <c r="L16">
+        <v>3.725</v>
+      </c>
+      <c r="M16">
+        <v>0.4664408000000001</v>
+      </c>
+      <c r="N16">
+        <v>3.2585592</v>
+      </c>
+      <c r="O16">
+        <v>0.8146397999999999</v>
+      </c>
+      <c r="P16">
+        <v>2.4439194</v>
+      </c>
+      <c r="Q16">
+        <v>2.4789194</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1155551000772359</v>
+      </c>
+      <c r="T16">
+        <v>0.8342453569895919</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.038325</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.986008085056022</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.10478087729423</v>
+      </c>
+      <c r="C17">
+        <v>58.84307804238263</v>
+      </c>
+      <c r="D17">
+        <v>57.12307804238263</v>
+      </c>
+      <c r="E17">
+        <v>-10.72</v>
+      </c>
+      <c r="F17">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="G17">
+        <v>11.5</v>
+      </c>
+      <c r="H17">
+        <v>44.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.76</v>
+      </c>
+      <c r="K17">
+        <v>0.035</v>
+      </c>
+      <c r="L17">
+        <v>3.725</v>
+      </c>
+      <c r="M17">
+        <v>0.51834</v>
+      </c>
+      <c r="N17">
+        <v>3.206659999999999</v>
+      </c>
+      <c r="O17">
+        <v>0.8016649999999998</v>
+      </c>
+      <c r="P17">
+        <v>2.404995</v>
+      </c>
+      <c r="Q17">
+        <v>2.439995</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1162569144638</v>
+      </c>
+      <c r="T17">
+        <v>0.8418733242891006</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>7.186402747231545</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1046193685220372</v>
+      </c>
+      <c r="C18">
+        <v>58.33124769769329</v>
+      </c>
+      <c r="D18">
+        <v>57.26324769769329</v>
+      </c>
+      <c r="E18">
+        <v>-10.068</v>
+      </c>
+      <c r="F18">
+        <v>10.432</v>
+      </c>
+      <c r="G18">
+        <v>11.5</v>
+      </c>
+      <c r="H18">
+        <v>44.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.76</v>
+      </c>
+      <c r="K18">
+        <v>0.035</v>
+      </c>
+      <c r="L18">
+        <v>3.725</v>
+      </c>
+      <c r="M18">
+        <v>0.5528960000000001</v>
+      </c>
+      <c r="N18">
+        <v>3.172104</v>
+      </c>
+      <c r="O18">
+        <v>0.7930259999999999</v>
+      </c>
+      <c r="P18">
+        <v>2.379078</v>
+      </c>
+      <c r="Q18">
+        <v>2.414078</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.116975438716711</v>
+      </c>
+      <c r="T18">
+        <v>0.8496829098576451</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>6.737252575529574</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1044578597498444</v>
+      </c>
+      <c r="C19">
+        <v>57.82010694687781</v>
+      </c>
+      <c r="D19">
+        <v>57.40410694687782</v>
+      </c>
+      <c r="E19">
+        <v>-9.415999999999999</v>
+      </c>
+      <c r="F19">
+        <v>11.084</v>
+      </c>
+      <c r="G19">
+        <v>11.5</v>
+      </c>
+      <c r="H19">
+        <v>44.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.76</v>
+      </c>
+      <c r="K19">
+        <v>0.035</v>
+      </c>
+      <c r="L19">
+        <v>3.725</v>
+      </c>
+      <c r="M19">
+        <v>0.5874520000000001</v>
+      </c>
+      <c r="N19">
+        <v>3.137548</v>
+      </c>
+      <c r="O19">
+        <v>0.7843869999999999</v>
+      </c>
+      <c r="P19">
+        <v>2.353161</v>
+      </c>
+      <c r="Q19">
+        <v>2.388161</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1177112768070415</v>
+      </c>
+      <c r="T19">
+        <v>0.8576806782109739</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.340943600498423</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1045663509776516</v>
+      </c>
+      <c r="C20">
+        <v>57.07341046529929</v>
+      </c>
+      <c r="D20">
+        <v>57.30941046529929</v>
+      </c>
+      <c r="E20">
+        <v>-8.763999999999999</v>
+      </c>
+      <c r="F20">
+        <v>11.736</v>
+      </c>
+      <c r="G20">
+        <v>11.5</v>
+      </c>
+      <c r="H20">
+        <v>44.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.76</v>
+      </c>
+      <c r="K20">
+        <v>0.035</v>
+      </c>
+      <c r="L20">
+        <v>3.725</v>
+      </c>
+      <c r="M20">
+        <v>0.6454800000000001</v>
+      </c>
+      <c r="N20">
+        <v>3.07952</v>
+      </c>
+      <c r="O20">
+        <v>0.7698799999999999</v>
+      </c>
+      <c r="P20">
+        <v>2.30964</v>
+      </c>
+      <c r="Q20">
+        <v>2.34464</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1184650621678678</v>
+      </c>
+      <c r="T20">
+        <v>0.8658735140851154</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.04125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.77089917580715</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1044198422054588</v>
+      </c>
+      <c r="C21">
+        <v>56.54936461880174</v>
+      </c>
+      <c r="D21">
+        <v>57.43736461880174</v>
+      </c>
+      <c r="E21">
+        <v>-8.112</v>
+      </c>
+      <c r="F21">
+        <v>12.388</v>
+      </c>
+      <c r="G21">
+        <v>11.5</v>
+      </c>
+      <c r="H21">
+        <v>44.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.76</v>
+      </c>
+      <c r="K21">
+        <v>0.035</v>
+      </c>
+      <c r="L21">
+        <v>3.725</v>
+      </c>
+      <c r="M21">
+        <v>0.6813399999999999</v>
+      </c>
+      <c r="N21">
+        <v>3.04366</v>
+      </c>
+      <c r="O21">
+        <v>0.7609149999999999</v>
+      </c>
+      <c r="P21">
+        <v>2.282745</v>
+      </c>
+      <c r="Q21">
+        <v>2.317745</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1192374595129121</v>
+      </c>
+      <c r="T21">
+        <v>0.8742686422030631</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.04125</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.467167640238354</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.104273333433266</v>
+      </c>
+      <c r="C22">
+        <v>56.0258914147815</v>
+      </c>
+      <c r="D22">
+        <v>57.5658914147815</v>
+      </c>
+      <c r="E22">
+        <v>-7.459999999999999</v>
+      </c>
+      <c r="F22">
+        <v>13.04</v>
+      </c>
+      <c r="G22">
+        <v>11.5</v>
+      </c>
+      <c r="H22">
+        <v>44.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.76</v>
+      </c>
+      <c r="K22">
+        <v>0.035</v>
+      </c>
+      <c r="L22">
+        <v>3.725</v>
+      </c>
+      <c r="M22">
+        <v>0.7172000000000001</v>
+      </c>
+      <c r="N22">
+        <v>3.0078</v>
+      </c>
+      <c r="O22">
+        <v>0.7519499999999999</v>
+      </c>
+      <c r="P22">
+        <v>2.25585</v>
+      </c>
+      <c r="Q22">
+        <v>2.29085</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1200291667915825</v>
+      </c>
+      <c r="T22">
+        <v>0.8828736485239593</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.04125</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.193809258226435</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1041268246610732</v>
+      </c>
+      <c r="C23">
+        <v>55.50299470604234</v>
+      </c>
+      <c r="D23">
+        <v>57.69499470604233</v>
+      </c>
+      <c r="E23">
+        <v>-6.808</v>
+      </c>
+      <c r="F23">
+        <v>13.692</v>
+      </c>
+      <c r="G23">
+        <v>11.5</v>
+      </c>
+      <c r="H23">
+        <v>44.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.76</v>
+      </c>
+      <c r="K23">
+        <v>0.035</v>
+      </c>
+      <c r="L23">
+        <v>3.725</v>
+      </c>
+      <c r="M23">
+        <v>0.7530600000000001</v>
+      </c>
+      <c r="N23">
+        <v>2.97194</v>
+      </c>
+      <c r="O23">
+        <v>0.7429849999999999</v>
+      </c>
+      <c r="P23">
+        <v>2.228955</v>
+      </c>
+      <c r="Q23">
+        <v>2.263955</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1208409172924977</v>
+      </c>
+      <c r="T23">
+        <v>0.8916965031061441</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.04125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.9464850078347</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1039803158888804</v>
+      </c>
+      <c r="C24">
+        <v>54.98067838002856</v>
+      </c>
+      <c r="D24">
+        <v>57.82467838002856</v>
+      </c>
+      <c r="E24">
+        <v>-6.155999999999999</v>
+      </c>
+      <c r="F24">
+        <v>14.344</v>
+      </c>
+      <c r="G24">
+        <v>11.5</v>
+      </c>
+      <c r="H24">
+        <v>44.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.76</v>
+      </c>
+      <c r="K24">
+        <v>0.035</v>
+      </c>
+      <c r="L24">
+        <v>3.725</v>
+      </c>
+      <c r="M24">
+        <v>0.7889200000000001</v>
+      </c>
+      <c r="N24">
+        <v>2.93608</v>
+      </c>
+      <c r="O24">
+        <v>0.7340199999999999</v>
+      </c>
+      <c r="P24">
+        <v>2.202059999999999</v>
+      </c>
+      <c r="Q24">
+        <v>2.23706</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.121673481908821</v>
+      </c>
+      <c r="T24">
+        <v>0.9007455847288978</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.04125</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.72164478020585</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1038338071166876</v>
+      </c>
+      <c r="C25">
+        <v>54.45894635921517</v>
+      </c>
+      <c r="D25">
+        <v>57.95494635921516</v>
+      </c>
+      <c r="E25">
+        <v>-5.504</v>
+      </c>
+      <c r="F25">
+        <v>14.996</v>
+      </c>
+      <c r="G25">
+        <v>11.5</v>
+      </c>
+      <c r="H25">
+        <v>44.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.76</v>
+      </c>
+      <c r="K25">
+        <v>0.035</v>
+      </c>
+      <c r="L25">
+        <v>3.725</v>
+      </c>
+      <c r="M25">
+        <v>0.8247800000000001</v>
+      </c>
+      <c r="N25">
+        <v>2.90022</v>
+      </c>
+      <c r="O25">
+        <v>0.7250549999999999</v>
+      </c>
+      <c r="P25">
+        <v>2.175165</v>
+      </c>
+      <c r="Q25">
+        <v>2.210165</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1225276715801137</v>
+      </c>
+      <c r="T25">
+        <v>0.9100297074327619</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.04125</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.51635587671864</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1043712983444948</v>
+      </c>
+      <c r="C26">
+        <v>53.3318867513901</v>
+      </c>
+      <c r="D26">
+        <v>57.4798867513901</v>
+      </c>
+      <c r="E26">
+        <v>-4.852</v>
+      </c>
+      <c r="F26">
+        <v>15.648</v>
+      </c>
+      <c r="G26">
+        <v>11.5</v>
+      </c>
+      <c r="H26">
+        <v>44.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.76</v>
+      </c>
+      <c r="K26">
+        <v>0.035</v>
+      </c>
+      <c r="L26">
+        <v>3.725</v>
+      </c>
+      <c r="M26">
+        <v>0.9201024000000001</v>
+      </c>
+      <c r="N26">
+        <v>2.804897599999999</v>
+      </c>
+      <c r="O26">
+        <v>0.7012243999999999</v>
+      </c>
+      <c r="P26">
+        <v>2.103673199999999</v>
+      </c>
+      <c r="Q26">
+        <v>2.138673199999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1234043399269668</v>
+      </c>
+      <c r="T26">
+        <v>0.9195581491551489</v>
+      </c>
+      <c r="U26">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.0441</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.048462432007566</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.105040789572302</v>
+      </c>
+      <c r="C27">
+        <v>52.0989413821716</v>
+      </c>
+      <c r="D27">
+        <v>56.8989413821716</v>
+      </c>
+      <c r="E27">
+        <v>-4.199999999999999</v>
+      </c>
+      <c r="F27">
+        <v>16.3</v>
+      </c>
+      <c r="G27">
+        <v>11.5</v>
+      </c>
+      <c r="H27">
+        <v>44.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.76</v>
+      </c>
+      <c r="K27">
+        <v>0.035</v>
+      </c>
+      <c r="L27">
+        <v>3.725</v>
+      </c>
+      <c r="M27">
+        <v>1.0269</v>
+      </c>
+      <c r="N27">
+        <v>2.698099999999999</v>
+      </c>
+      <c r="O27">
+        <v>0.6745249999999998</v>
+      </c>
+      <c r="P27">
+        <v>2.023574999999999</v>
+      </c>
+      <c r="Q27">
+        <v>2.058574999999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1243043860964026</v>
+      </c>
+      <c r="T27">
+        <v>0.9293406826567994</v>
+      </c>
+      <c r="U27">
+        <v>0.063</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.04725</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.62742233907878</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1063387808001092</v>
+      </c>
+      <c r="C28">
+        <v>50.35343146223157</v>
+      </c>
+      <c r="D28">
+        <v>55.80543146223157</v>
+      </c>
+      <c r="E28">
+        <v>-3.547999999999998</v>
+      </c>
+      <c r="F28">
+        <v>16.952</v>
+      </c>
+      <c r="G28">
+        <v>11.5</v>
+      </c>
+      <c r="H28">
+        <v>44.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.76</v>
+      </c>
+      <c r="K28">
+        <v>0.035</v>
+      </c>
+      <c r="L28">
+        <v>3.725</v>
+      </c>
+      <c r="M28">
+        <v>1.1883352</v>
+      </c>
+      <c r="N28">
+        <v>2.5366648</v>
+      </c>
+      <c r="O28">
+        <v>0.6341661999999999</v>
+      </c>
+      <c r="P28">
+        <v>1.9024986</v>
+      </c>
+      <c r="Q28">
+        <v>1.9374986</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1252287578379854</v>
+      </c>
+      <c r="T28">
+        <v>0.9393876089557918</v>
+      </c>
+      <c r="U28">
+        <v>0.0701</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.052575</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>3.134637432266586</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1063055220279163</v>
+      </c>
+      <c r="C29">
+        <v>49.72892580752908</v>
+      </c>
+      <c r="D29">
+        <v>55.83292580752908</v>
+      </c>
+      <c r="E29">
+        <v>-2.895999999999997</v>
+      </c>
+      <c r="F29">
+        <v>17.604</v>
+      </c>
+      <c r="G29">
+        <v>11.5</v>
+      </c>
+      <c r="H29">
+        <v>44.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.76</v>
+      </c>
+      <c r="K29">
+        <v>0.035</v>
+      </c>
+      <c r="L29">
+        <v>3.725</v>
+      </c>
+      <c r="M29">
+        <v>1.2340404</v>
+      </c>
+      <c r="N29">
+        <v>2.4909596</v>
+      </c>
+      <c r="O29">
+        <v>0.6227398999999999</v>
+      </c>
+      <c r="P29">
+        <v>1.8682197</v>
+      </c>
+      <c r="Q29">
+        <v>1.9032197</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1261784548327621</v>
+      </c>
+      <c r="T29">
+        <v>0.9497097935095512</v>
+      </c>
+      <c r="U29">
+        <v>0.0701</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.052575</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.018539749590046</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1107452632557236</v>
+      </c>
+      <c r="C30">
+        <v>45.63147670693013</v>
+      </c>
+      <c r="D30">
+        <v>52.38747670693013</v>
+      </c>
+      <c r="E30">
+        <v>-2.243999999999996</v>
+      </c>
+      <c r="F30">
+        <v>18.256</v>
+      </c>
+      <c r="G30">
+        <v>11.5</v>
+      </c>
+      <c r="H30">
+        <v>44.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.76</v>
+      </c>
+      <c r="K30">
+        <v>0.035</v>
+      </c>
+      <c r="L30">
+        <v>3.725</v>
+      </c>
+      <c r="M30">
+        <v>1.6685984</v>
+      </c>
+      <c r="N30">
+        <v>2.056401599999999</v>
+      </c>
+      <c r="O30">
+        <v>0.5141003999999998</v>
+      </c>
+      <c r="P30">
+        <v>1.542301199999999</v>
+      </c>
+      <c r="Q30">
+        <v>1.577301199999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.127154532299616</v>
+      </c>
+      <c r="T30">
+        <v>0.960318705412026</v>
+      </c>
+      <c r="U30">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.06855</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.232412544564347</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1108717544835307</v>
+      </c>
+      <c r="C31">
+        <v>44.88753283380165</v>
+      </c>
+      <c r="D31">
+        <v>52.29553283380165</v>
+      </c>
+      <c r="E31">
+        <v>-1.591999999999999</v>
+      </c>
+      <c r="F31">
+        <v>18.908</v>
+      </c>
+      <c r="G31">
+        <v>11.5</v>
+      </c>
+      <c r="H31">
+        <v>44.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.76</v>
+      </c>
+      <c r="K31">
+        <v>0.035</v>
+      </c>
+      <c r="L31">
+        <v>3.725</v>
+      </c>
+      <c r="M31">
+        <v>1.7281912</v>
+      </c>
+      <c r="N31">
+        <v>1.996808799999999</v>
+      </c>
+      <c r="O31">
+        <v>0.4992021999999998</v>
+      </c>
+      <c r="P31">
+        <v>1.497606599999999</v>
+      </c>
+      <c r="Q31">
+        <v>1.532606599999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1281581049063814</v>
+      </c>
+      <c r="T31">
+        <v>0.9712264599033029</v>
+      </c>
+      <c r="U31">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.06855</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.155432801648336</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.110998245711338</v>
+      </c>
+      <c r="C32">
+        <v>44.14391113175327</v>
+      </c>
+      <c r="D32">
+        <v>52.20391113175327</v>
+      </c>
+      <c r="E32">
+        <v>-0.9400000000000013</v>
+      </c>
+      <c r="F32">
+        <v>19.56</v>
+      </c>
+      <c r="G32">
+        <v>11.5</v>
+      </c>
+      <c r="H32">
+        <v>44.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.76</v>
+      </c>
+      <c r="K32">
+        <v>0.035</v>
+      </c>
+      <c r="L32">
+        <v>3.725</v>
+      </c>
+      <c r="M32">
+        <v>1.787784</v>
+      </c>
+      <c r="N32">
+        <v>1.937216</v>
+      </c>
+      <c r="O32">
+        <v>0.4843039999999999</v>
+      </c>
+      <c r="P32">
+        <v>1.452912</v>
+      </c>
+      <c r="Q32">
+        <v>1.487912</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1291903510161971</v>
+      </c>
+      <c r="T32">
+        <v>0.9824458645229021</v>
+      </c>
+      <c r="U32">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.06855</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.083585041593391</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1111247369391451</v>
+      </c>
+      <c r="C33">
+        <v>43.40060991041668</v>
+      </c>
+      <c r="D33">
+        <v>52.11260991041668</v>
+      </c>
+      <c r="E33">
+        <v>-0.2880000000000003</v>
+      </c>
+      <c r="F33">
+        <v>20.212</v>
+      </c>
+      <c r="G33">
+        <v>11.5</v>
+      </c>
+      <c r="H33">
+        <v>44.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.76</v>
+      </c>
+      <c r="K33">
+        <v>0.035</v>
+      </c>
+      <c r="L33">
+        <v>3.725</v>
+      </c>
+      <c r="M33">
+        <v>1.8473768</v>
+      </c>
+      <c r="N33">
+        <v>1.877623199999999</v>
+      </c>
+      <c r="O33">
+        <v>0.4694057999999999</v>
+      </c>
+      <c r="P33">
+        <v>1.4082174</v>
+      </c>
+      <c r="Q33">
+        <v>1.4432174</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1302525173031089</v>
+      </c>
+      <c r="T33">
+        <v>0.9939904692764027</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.06855</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.01637262089683</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1163152281669523</v>
+      </c>
+      <c r="C34">
+        <v>39.25910144872996</v>
+      </c>
+      <c r="D34">
+        <v>48.62310144872996</v>
+      </c>
+      <c r="E34">
+        <v>0.3640000000000008</v>
+      </c>
+      <c r="F34">
+        <v>20.864</v>
+      </c>
+      <c r="G34">
+        <v>11.5</v>
+      </c>
+      <c r="H34">
+        <v>44.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.76</v>
+      </c>
+      <c r="K34">
+        <v>0.035</v>
+      </c>
+      <c r="L34">
+        <v>3.725</v>
+      </c>
+      <c r="M34">
+        <v>2.3472</v>
+      </c>
+      <c r="N34">
+        <v>1.3778</v>
+      </c>
+      <c r="O34">
+        <v>0.3444499999999999</v>
+      </c>
+      <c r="P34">
+        <v>1.03335</v>
+      </c>
+      <c r="Q34">
+        <v>1.06835</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1313459237749299</v>
+      </c>
+      <c r="T34">
+        <v>1.005874621228536</v>
+      </c>
+      <c r="U34">
+        <v>0.1125</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>1.586997273346967</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1165999693947595</v>
+      </c>
+      <c r="C35">
+        <v>38.42914505987774</v>
+      </c>
+      <c r="D35">
+        <v>48.44514505987774</v>
+      </c>
+      <c r="E35">
+        <v>1.016000000000002</v>
+      </c>
+      <c r="F35">
+        <v>21.516</v>
+      </c>
+      <c r="G35">
+        <v>11.5</v>
+      </c>
+      <c r="H35">
+        <v>44.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.76</v>
+      </c>
+      <c r="K35">
+        <v>0.035</v>
+      </c>
+      <c r="L35">
+        <v>3.725</v>
+      </c>
+      <c r="M35">
+        <v>2.42055</v>
+      </c>
+      <c r="N35">
+        <v>1.304449999999999</v>
+      </c>
+      <c r="O35">
+        <v>0.3261124999999998</v>
+      </c>
+      <c r="P35">
+        <v>0.9783374999999994</v>
+      </c>
+      <c r="Q35">
+        <v>1.013337499999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1324719692459098</v>
+      </c>
+      <c r="T35">
+        <v>1.01811352398521</v>
+      </c>
+      <c r="U35">
+        <v>0.1125</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.538906446881906</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1416030235559708</v>
+      </c>
+      <c r="C36">
+        <v>25.99464544185449</v>
+      </c>
+      <c r="D36">
+        <v>36.66264544185449</v>
+      </c>
+      <c r="E36">
+        <v>1.668000000000003</v>
+      </c>
+      <c r="F36">
+        <v>22.168</v>
+      </c>
+      <c r="G36">
+        <v>11.5</v>
+      </c>
+      <c r="H36">
+        <v>44.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.76</v>
+      </c>
+      <c r="K36">
+        <v>0.035</v>
+      </c>
+      <c r="L36">
+        <v>3.725</v>
+      </c>
+      <c r="M36">
+        <v>4.358228800000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.6332288000000013</v>
+      </c>
+      <c r="O36">
+        <v>-0.1583072000000003</v>
+      </c>
+      <c r="P36">
+        <v>-0.4749216000000009</v>
+      </c>
+      <c r="Q36">
+        <v>-0.4399216000000009</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1349121197213538</v>
+      </c>
+      <c r="T36">
+        <v>1.044635334294189</v>
+      </c>
+      <c r="U36">
+        <v>0.1966</v>
+      </c>
+      <c r="V36">
+        <v>0.2136762530686777</v>
+      </c>
+      <c r="W36">
+        <v>0.154591248646698</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.854705012274711</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1431810235559708</v>
+      </c>
+      <c r="C37">
+        <v>24.78839091803077</v>
+      </c>
+      <c r="D37">
+        <v>36.10839091803078</v>
+      </c>
+      <c r="E37">
+        <v>2.320000000000004</v>
+      </c>
+      <c r="F37">
+        <v>22.82</v>
+      </c>
+      <c r="G37">
+        <v>11.5</v>
+      </c>
+      <c r="H37">
+        <v>44.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.76</v>
+      </c>
+      <c r="K37">
+        <v>0.035</v>
+      </c>
+      <c r="L37">
+        <v>3.725</v>
+      </c>
+      <c r="M37">
+        <v>4.486412000000001</v>
+      </c>
+      <c r="N37">
+        <v>-0.7614120000000009</v>
+      </c>
+      <c r="O37">
+        <v>-0.1903530000000002</v>
+      </c>
+      <c r="P37">
+        <v>-0.5710590000000006</v>
+      </c>
+      <c r="Q37">
+        <v>-0.5360590000000006</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.136390767717067</v>
+      </c>
+      <c r="T37">
+        <v>1.060706647129484</v>
+      </c>
+      <c r="U37">
+        <v>0.1966</v>
+      </c>
+      <c r="V37">
+        <v>0.2075712172667155</v>
+      </c>
+      <c r="W37">
+        <v>0.1557914986853637</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.8302848690668622</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1447590235559708</v>
+      </c>
+      <c r="C38">
+        <v>23.59864492003605</v>
+      </c>
+      <c r="D38">
+        <v>35.57064492003605</v>
+      </c>
+      <c r="E38">
+        <v>2.972000000000001</v>
+      </c>
+      <c r="F38">
+        <v>23.472</v>
+      </c>
+      <c r="G38">
+        <v>11.5</v>
+      </c>
+      <c r="H38">
+        <v>44.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.76</v>
+      </c>
+      <c r="K38">
+        <v>0.035</v>
+      </c>
+      <c r="L38">
+        <v>3.725</v>
+      </c>
+      <c r="M38">
+        <v>4.6145952</v>
+      </c>
+      <c r="N38">
+        <v>-0.8895952000000005</v>
+      </c>
+      <c r="O38">
+        <v>-0.2223988000000001</v>
+      </c>
+      <c r="P38">
+        <v>-0.6671964000000004</v>
+      </c>
+      <c r="Q38">
+        <v>-0.6321964000000003</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1379156234626461</v>
+      </c>
+      <c r="T38">
+        <v>1.077280188490882</v>
+      </c>
+      <c r="U38">
+        <v>0.1966</v>
+      </c>
+      <c r="V38">
+        <v>0.2018053501204179</v>
+      </c>
+      <c r="W38">
+        <v>0.1569250681663258</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.8072214004816716</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1531008157431069</v>
+      </c>
+      <c r="C39">
+        <v>20.35066232834364</v>
+      </c>
+      <c r="D39">
+        <v>32.97466232834364</v>
+      </c>
+      <c r="E39">
+        <v>3.624000000000002</v>
+      </c>
+      <c r="F39">
+        <v>24.124</v>
+      </c>
+      <c r="G39">
+        <v>11.5</v>
+      </c>
+      <c r="H39">
+        <v>44.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.76</v>
+      </c>
+      <c r="K39">
+        <v>0.035</v>
+      </c>
+      <c r="L39">
+        <v>3.725</v>
+      </c>
+      <c r="M39">
+        <v>5.1577112</v>
+      </c>
+      <c r="N39">
+        <v>-1.432711200000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.3581778000000002</v>
+      </c>
+      <c r="P39">
+        <v>-1.074533400000001</v>
+      </c>
+      <c r="Q39">
+        <v>-1.039533400000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1401234781003644</v>
+      </c>
+      <c r="T39">
+        <v>1.101277192970989</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1805548941941534</v>
+      </c>
+      <c r="W39">
+        <v>0.17519736362129</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.7222195767766135</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1548508157431069</v>
+      </c>
+      <c r="C40">
+        <v>19.20141757650716</v>
+      </c>
+      <c r="D40">
+        <v>32.47741757650716</v>
+      </c>
+      <c r="E40">
+        <v>4.276</v>
+      </c>
+      <c r="F40">
+        <v>24.776</v>
+      </c>
+      <c r="G40">
+        <v>11.5</v>
+      </c>
+      <c r="H40">
+        <v>44.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.76</v>
+      </c>
+      <c r="K40">
+        <v>0.035</v>
+      </c>
+      <c r="L40">
+        <v>3.725</v>
+      </c>
+      <c r="M40">
+        <v>5.297108799999999</v>
+      </c>
+      <c r="N40">
+        <v>-1.5721088</v>
+      </c>
+      <c r="O40">
+        <v>-0.3930271999999999</v>
+      </c>
+      <c r="P40">
+        <v>-1.1790816</v>
+      </c>
+      <c r="Q40">
+        <v>-1.1440816</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1417577277471445</v>
+      </c>
+      <c r="T40">
+        <v>1.119039728341489</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1758034496100968</v>
+      </c>
+      <c r="W40">
+        <v>0.1762132224733613</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.703213798440387</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1566008157431069</v>
+      </c>
+      <c r="C41">
+        <v>18.06694654775952</v>
+      </c>
+      <c r="D41">
+        <v>31.99494654775952</v>
+      </c>
+      <c r="E41">
+        <v>4.928000000000001</v>
+      </c>
+      <c r="F41">
+        <v>25.428</v>
+      </c>
+      <c r="G41">
+        <v>11.5</v>
+      </c>
+      <c r="H41">
+        <v>44.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.76</v>
+      </c>
+      <c r="K41">
+        <v>0.035</v>
+      </c>
+      <c r="L41">
+        <v>3.725</v>
+      </c>
+      <c r="M41">
+        <v>5.4365064</v>
+      </c>
+      <c r="N41">
+        <v>-1.7115064</v>
+      </c>
+      <c r="O41">
+        <v>-0.4278766000000001</v>
+      </c>
+      <c r="P41">
+        <v>-1.2836298</v>
+      </c>
+      <c r="Q41">
+        <v>-1.2486298</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1434455593495567</v>
+      </c>
+      <c r="T41">
+        <v>1.137384641920857</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1712956688508635</v>
+      </c>
+      <c r="W41">
+        <v>0.1771769859996854</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.6851826754034539</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1583508157431069</v>
+      </c>
+      <c r="C42">
+        <v>16.94660046320504</v>
+      </c>
+      <c r="D42">
+        <v>31.52660046320504</v>
+      </c>
+      <c r="E42">
+        <v>5.580000000000002</v>
+      </c>
+      <c r="F42">
+        <v>26.08</v>
+      </c>
+      <c r="G42">
+        <v>11.5</v>
+      </c>
+      <c r="H42">
+        <v>44.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.76</v>
+      </c>
+      <c r="K42">
+        <v>0.035</v>
+      </c>
+      <c r="L42">
+        <v>3.725</v>
+      </c>
+      <c r="M42">
+        <v>5.575904</v>
+      </c>
+      <c r="N42">
+        <v>-1.850904000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.4627260000000002</v>
+      </c>
+      <c r="P42">
+        <v>-1.388178000000001</v>
+      </c>
+      <c r="Q42">
+        <v>-1.353178000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1451896520053826</v>
+      </c>
+      <c r="T42">
+        <v>1.156341052619538</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1670132771295919</v>
+      </c>
+      <c r="W42">
+        <v>0.1780925613496932</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.6680531085183674</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1601008157431069</v>
+      </c>
+      <c r="C43">
+        <v>15.83976798353357</v>
+      </c>
+      <c r="D43">
+        <v>31.07176798353357</v>
+      </c>
+      <c r="E43">
+        <v>6.232000000000003</v>
+      </c>
+      <c r="F43">
+        <v>26.732</v>
+      </c>
+      <c r="G43">
+        <v>11.5</v>
+      </c>
+      <c r="H43">
+        <v>44.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.76</v>
+      </c>
+      <c r="K43">
+        <v>0.035</v>
+      </c>
+      <c r="L43">
+        <v>3.725</v>
+      </c>
+      <c r="M43">
+        <v>5.7153016</v>
+      </c>
+      <c r="N43">
+        <v>-1.9903016</v>
+      </c>
+      <c r="O43">
+        <v>-0.4975754000000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.4927262</v>
+      </c>
+      <c r="Q43">
+        <v>-1.4577262</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1469928664461518</v>
+      </c>
+      <c r="T43">
+        <v>1.175940053511395</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1629397825654555</v>
+      </c>
+      <c r="W43">
+        <v>0.1789634744875056</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.651759130261822</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1618508157431069</v>
+      </c>
+      <c r="C44">
+        <v>14.7458725467353</v>
+      </c>
+      <c r="D44">
+        <v>30.6298725467353</v>
+      </c>
+      <c r="E44">
+        <v>6.884</v>
+      </c>
+      <c r="F44">
+        <v>27.384</v>
+      </c>
+      <c r="G44">
+        <v>11.5</v>
+      </c>
+      <c r="H44">
+        <v>44.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.76</v>
+      </c>
+      <c r="K44">
+        <v>0.035</v>
+      </c>
+      <c r="L44">
+        <v>3.725</v>
+      </c>
+      <c r="M44">
+        <v>5.8546992</v>
+      </c>
+      <c r="N44">
+        <v>-2.1296992</v>
+      </c>
+      <c r="O44">
+        <v>-0.5324248</v>
+      </c>
+      <c r="P44">
+        <v>-1.5972744</v>
+      </c>
+      <c r="Q44">
+        <v>-1.5622744</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1488582606952234</v>
+      </c>
+      <c r="T44">
+        <v>1.196214882020212</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1590602639329446</v>
+      </c>
+      <c r="W44">
+        <v>0.1797929155711364</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.6362410557317786</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1636008157431069</v>
+      </c>
+      <c r="C45">
+        <v>13.66436992980431</v>
+      </c>
+      <c r="D45">
+        <v>30.20036992980431</v>
+      </c>
+      <c r="E45">
+        <v>7.536000000000001</v>
+      </c>
+      <c r="F45">
+        <v>28.036</v>
+      </c>
+      <c r="G45">
+        <v>11.5</v>
+      </c>
+      <c r="H45">
+        <v>44.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.76</v>
+      </c>
+      <c r="K45">
+        <v>0.035</v>
+      </c>
+      <c r="L45">
+        <v>3.725</v>
+      </c>
+      <c r="M45">
+        <v>5.9940968</v>
+      </c>
+      <c r="N45">
+        <v>-2.269096800000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.5672742000000002</v>
+      </c>
+      <c r="P45">
+        <v>-1.701822600000001</v>
+      </c>
+      <c r="Q45">
+        <v>-1.666822600000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.150789107374087</v>
+      </c>
+      <c r="T45">
+        <v>1.217201108020566</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1553611880275273</v>
+      </c>
+      <c r="W45">
+        <v>0.1805837779997146</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6214447521101093</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1653508157431069</v>
+      </c>
+      <c r="C46">
+        <v>12.59474601274918</v>
+      </c>
+      <c r="D46">
+        <v>29.78274601274918</v>
+      </c>
+      <c r="E46">
+        <v>8.188000000000002</v>
+      </c>
+      <c r="F46">
+        <v>28.688</v>
+      </c>
+      <c r="G46">
+        <v>11.5</v>
+      </c>
+      <c r="H46">
+        <v>44.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.76</v>
+      </c>
+      <c r="K46">
+        <v>0.035</v>
+      </c>
+      <c r="L46">
+        <v>3.725</v>
+      </c>
+      <c r="M46">
+        <v>6.1334944</v>
+      </c>
+      <c r="N46">
+        <v>-2.4084944</v>
+      </c>
+      <c r="O46">
+        <v>-0.6021236000000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.8063708</v>
+      </c>
+      <c r="Q46">
+        <v>-1.7713708</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.15278891286291</v>
+      </c>
+      <c r="T46">
+        <v>1.238936842092362</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1518302519359926</v>
+      </c>
+      <c r="W46">
+        <v>0.1813386921360848</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6073210077439705</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1671008157431069</v>
+      </c>
+      <c r="C47">
+        <v>11.53651472559456</v>
+      </c>
+      <c r="D47">
+        <v>29.37651472559456</v>
+      </c>
+      <c r="E47">
+        <v>8.840000000000003</v>
+      </c>
+      <c r="F47">
+        <v>29.34</v>
+      </c>
+      <c r="G47">
+        <v>11.5</v>
+      </c>
+      <c r="H47">
+        <v>44.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.76</v>
+      </c>
+      <c r="K47">
+        <v>0.035</v>
+      </c>
+      <c r="L47">
+        <v>3.725</v>
+      </c>
+      <c r="M47">
+        <v>6.272892000000001</v>
+      </c>
+      <c r="N47">
+        <v>-2.547892000000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.6369730000000002</v>
+      </c>
+      <c r="P47">
+        <v>-1.910919000000001</v>
+      </c>
+      <c r="Q47">
+        <v>-1.875919000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1548614385513265</v>
+      </c>
+      <c r="T47">
+        <v>1.261462966494042</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.148456246337415</v>
+      </c>
+      <c r="W47">
+        <v>0.1820600545330607</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.59382498534966</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1688508157431069</v>
+      </c>
+      <c r="C48">
+        <v>10.48921616113696</v>
+      </c>
+      <c r="D48">
+        <v>28.98121616113695</v>
+      </c>
+      <c r="E48">
+        <v>9.492000000000001</v>
+      </c>
+      <c r="F48">
+        <v>29.992</v>
+      </c>
+      <c r="G48">
+        <v>11.5</v>
+      </c>
+      <c r="H48">
+        <v>44.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.76</v>
+      </c>
+      <c r="K48">
+        <v>0.035</v>
+      </c>
+      <c r="L48">
+        <v>3.725</v>
+      </c>
+      <c r="M48">
+        <v>6.4122896</v>
+      </c>
+      <c r="N48">
+        <v>-2.687289600000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.6718224000000002</v>
+      </c>
+      <c r="P48">
+        <v>-2.015467200000001</v>
+      </c>
+      <c r="Q48">
+        <v>-1.980467200000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1570107244504252</v>
+      </c>
+      <c r="T48">
+        <v>1.284823391799487</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1452289366344277</v>
+      </c>
+      <c r="W48">
+        <v>0.1827500533475593</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5809157465377108</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1706008157431069</v>
+      </c>
+      <c r="C49">
+        <v>9.452414838049226</v>
+      </c>
+      <c r="D49">
+        <v>28.59641483804922</v>
+      </c>
+      <c r="E49">
+        <v>10.144</v>
+      </c>
+      <c r="F49">
+        <v>30.644</v>
+      </c>
+      <c r="G49">
+        <v>11.5</v>
+      </c>
+      <c r="H49">
+        <v>44.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.76</v>
+      </c>
+      <c r="K49">
+        <v>0.035</v>
+      </c>
+      <c r="L49">
+        <v>3.725</v>
+      </c>
+      <c r="M49">
+        <v>6.5516872</v>
+      </c>
+      <c r="N49">
+        <v>-2.8266872</v>
+      </c>
+      <c r="O49">
+        <v>-0.7066718000000001</v>
+      </c>
+      <c r="P49">
+        <v>-2.1200154</v>
+      </c>
+      <c r="Q49">
+        <v>-2.0850154</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1592411154777917</v>
+      </c>
+      <c r="T49">
+        <v>1.309065342588156</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1421389592592271</v>
+      </c>
+      <c r="W49">
+        <v>0.1834106905103772</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5685558370369086</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1723508157431069</v>
+      </c>
+      <c r="C50">
+        <v>8.425698100542746</v>
+      </c>
+      <c r="D50">
+        <v>28.22169810054275</v>
+      </c>
+      <c r="E50">
+        <v>10.796</v>
+      </c>
+      <c r="F50">
+        <v>31.296</v>
+      </c>
+      <c r="G50">
+        <v>11.5</v>
+      </c>
+      <c r="H50">
+        <v>44.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.76</v>
+      </c>
+      <c r="K50">
+        <v>0.035</v>
+      </c>
+      <c r="L50">
+        <v>3.725</v>
+      </c>
+      <c r="M50">
+        <v>6.6910848</v>
+      </c>
+      <c r="N50">
+        <v>-2.9660848</v>
+      </c>
+      <c r="O50">
+        <v>-0.7415212</v>
+      </c>
+      <c r="P50">
+        <v>-2.2245636</v>
+      </c>
+      <c r="Q50">
+        <v>-2.1895636</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1615572907754415</v>
+      </c>
+      <c r="T50">
+        <v>1.334239676099467</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1391777309413266</v>
+      </c>
+      <c r="W50">
+        <v>0.1840438011247444</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5567109237653063</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1741008157431069</v>
+      </c>
+      <c r="C51">
+        <v>7.408674642223602</v>
+      </c>
+      <c r="D51">
+        <v>27.8566746422236</v>
+      </c>
+      <c r="E51">
+        <v>11.448</v>
+      </c>
+      <c r="F51">
+        <v>31.948</v>
+      </c>
+      <c r="G51">
+        <v>11.5</v>
+      </c>
+      <c r="H51">
+        <v>44.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.76</v>
+      </c>
+      <c r="K51">
+        <v>0.035</v>
+      </c>
+      <c r="L51">
+        <v>3.725</v>
+      </c>
+      <c r="M51">
+        <v>6.8304824</v>
+      </c>
+      <c r="N51">
+        <v>-3.105482400000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.7763706000000001</v>
+      </c>
+      <c r="P51">
+        <v>-2.329111800000001</v>
+      </c>
+      <c r="Q51">
+        <v>-2.2941118</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1639642964769207</v>
+      </c>
+      <c r="T51">
+        <v>1.360401238375927</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1363373690853811</v>
+      </c>
+      <c r="W51">
+        <v>0.1846510704895455</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5453494763415245</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1758508157431069</v>
+      </c>
+      <c r="C52">
+        <v>6.400973143041952</v>
+      </c>
+      <c r="D52">
+        <v>27.50097314304195</v>
+      </c>
+      <c r="E52">
+        <v>12.1</v>
+      </c>
+      <c r="F52">
+        <v>32.6</v>
+      </c>
+      <c r="G52">
+        <v>11.5</v>
+      </c>
+      <c r="H52">
+        <v>44.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.76</v>
+      </c>
+      <c r="K52">
+        <v>0.035</v>
+      </c>
+      <c r="L52">
+        <v>3.725</v>
+      </c>
+      <c r="M52">
+        <v>6.96988</v>
+      </c>
+      <c r="N52">
+        <v>-3.24488</v>
+      </c>
+      <c r="O52">
+        <v>-0.8112200000000001</v>
+      </c>
+      <c r="P52">
+        <v>-2.43366</v>
+      </c>
+      <c r="Q52">
+        <v>-2.39866</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1664675824064592</v>
+      </c>
+      <c r="T52">
+        <v>1.387609263143446</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1336106217036735</v>
+      </c>
+      <c r="W52">
+        <v>0.1852340490797546</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.534442486814694</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1776008157431069</v>
+      </c>
+      <c r="C53">
+        <v>5.402241009353368</v>
+      </c>
+      <c r="D53">
+        <v>27.15424100935337</v>
+      </c>
+      <c r="E53">
+        <v>12.752</v>
+      </c>
+      <c r="F53">
+        <v>33.252</v>
+      </c>
+      <c r="G53">
+        <v>11.5</v>
+      </c>
+      <c r="H53">
+        <v>44.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.76</v>
+      </c>
+      <c r="K53">
+        <v>0.035</v>
+      </c>
+      <c r="L53">
+        <v>3.725</v>
+      </c>
+      <c r="M53">
+        <v>7.1092776</v>
+      </c>
+      <c r="N53">
+        <v>-3.384277600000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.8460694000000002</v>
+      </c>
+      <c r="P53">
+        <v>-2.538208200000001</v>
+      </c>
+      <c r="Q53">
+        <v>-2.5032082</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1690730432718971</v>
+      </c>
+      <c r="T53">
+        <v>1.415927819534128</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1309908055918368</v>
+      </c>
+      <c r="W53">
+        <v>0.1857941657644653</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.523963222367347</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1793508157431069</v>
+      </c>
+      <c r="C54">
+        <v>4.412143208105284</v>
+      </c>
+      <c r="D54">
+        <v>26.81614320810528</v>
+      </c>
+      <c r="E54">
+        <v>13.404</v>
+      </c>
+      <c r="F54">
+        <v>33.904</v>
+      </c>
+      <c r="G54">
+        <v>11.5</v>
+      </c>
+      <c r="H54">
+        <v>44.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.76</v>
+      </c>
+      <c r="K54">
+        <v>0.035</v>
+      </c>
+      <c r="L54">
+        <v>3.725</v>
+      </c>
+      <c r="M54">
+        <v>7.2486752</v>
+      </c>
+      <c r="N54">
+        <v>-3.5236752</v>
+      </c>
+      <c r="O54">
+        <v>-0.8809188000000001</v>
+      </c>
+      <c r="P54">
+        <v>-2.642756400000001</v>
+      </c>
+      <c r="Q54">
+        <v>-2.6077564</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1717870650067283</v>
+      </c>
+      <c r="T54">
+        <v>1.445426315774423</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1284717516381476</v>
+      </c>
+      <c r="W54">
+        <v>0.186332739499764</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5138870065525905</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1811008157431069</v>
+      </c>
+      <c r="C55">
+        <v>3.43036118704574</v>
+      </c>
+      <c r="D55">
+        <v>26.48636118704574</v>
+      </c>
+      <c r="E55">
+        <v>14.056</v>
+      </c>
+      <c r="F55">
+        <v>34.556</v>
+      </c>
+      <c r="G55">
+        <v>11.5</v>
+      </c>
+      <c r="H55">
+        <v>44.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.76</v>
+      </c>
+      <c r="K55">
+        <v>0.035</v>
+      </c>
+      <c r="L55">
+        <v>3.725</v>
+      </c>
+      <c r="M55">
+        <v>7.388072800000001</v>
+      </c>
+      <c r="N55">
+        <v>-3.663072800000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.9157682000000003</v>
+      </c>
+      <c r="P55">
+        <v>-2.747304600000001</v>
+      </c>
+      <c r="Q55">
+        <v>-2.7123046</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1746165770281481</v>
+      </c>
+      <c r="T55">
+        <v>1.476180067173879</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1260477563242203</v>
+      </c>
+      <c r="W55">
+        <v>0.1868509896978817</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5041910252968811</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1968292200221995</v>
+      </c>
+      <c r="C56">
+        <v>0.1422145518006701</v>
+      </c>
+      <c r="D56">
+        <v>23.85021455180068</v>
+      </c>
+      <c r="E56">
+        <v>14.70800000000001</v>
+      </c>
+      <c r="F56">
+        <v>35.20800000000001</v>
+      </c>
+      <c r="G56">
+        <v>11.5</v>
+      </c>
+      <c r="H56">
+        <v>44.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.76</v>
+      </c>
+      <c r="K56">
+        <v>0.035</v>
+      </c>
+      <c r="L56">
+        <v>3.725</v>
+      </c>
+      <c r="M56">
+        <v>8.407670400000002</v>
+      </c>
+      <c r="N56">
+        <v>-4.682670400000003</v>
+      </c>
+      <c r="O56">
+        <v>-1.170667600000001</v>
+      </c>
+      <c r="P56">
+        <v>-3.512002800000002</v>
+      </c>
+      <c r="Q56">
+        <v>-3.477002800000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1786091206137439</v>
+      </c>
+      <c r="T56">
+        <v>1.519574720369696</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1107619537511841</v>
+      </c>
+      <c r="W56">
+        <v>0.2123500454442172</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4430478150047364</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1988292200221995</v>
+      </c>
+      <c r="C57">
+        <v>-0.8078586944288801</v>
+      </c>
+      <c r="D57">
+        <v>23.55214130557112</v>
+      </c>
+      <c r="E57">
+        <v>15.36000000000001</v>
+      </c>
+      <c r="F57">
+        <v>35.86000000000001</v>
+      </c>
+      <c r="G57">
+        <v>11.5</v>
+      </c>
+      <c r="H57">
+        <v>44.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.76</v>
+      </c>
+      <c r="K57">
+        <v>0.035</v>
+      </c>
+      <c r="L57">
+        <v>3.725</v>
+      </c>
+      <c r="M57">
+        <v>8.563368000000002</v>
+      </c>
+      <c r="N57">
+        <v>-4.838368000000003</v>
+      </c>
+      <c r="O57">
+        <v>-1.209592000000001</v>
+      </c>
+      <c r="P57">
+        <v>-3.628776000000002</v>
+      </c>
+      <c r="Q57">
+        <v>-3.593776000000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.181715989960716</v>
+      </c>
+      <c r="T57">
+        <v>1.553343047489023</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.1087481000466171</v>
+      </c>
+      <c r="W57">
+        <v>0.2128309537088678</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.4349924001864686</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2008292200221995</v>
+      </c>
+      <c r="C58">
+        <v>-1.750573434675673</v>
+      </c>
+      <c r="D58">
+        <v>23.26142656532434</v>
+      </c>
+      <c r="E58">
+        <v>16.01200000000001</v>
+      </c>
+      <c r="F58">
+        <v>36.51200000000001</v>
+      </c>
+      <c r="G58">
+        <v>11.5</v>
+      </c>
+      <c r="H58">
+        <v>44.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.76</v>
+      </c>
+      <c r="K58">
+        <v>0.035</v>
+      </c>
+      <c r="L58">
+        <v>3.725</v>
+      </c>
+      <c r="M58">
+        <v>8.719065600000002</v>
+      </c>
+      <c r="N58">
+        <v>-4.994065600000003</v>
+      </c>
+      <c r="O58">
+        <v>-1.248516400000001</v>
+      </c>
+      <c r="P58">
+        <v>-3.745549200000002</v>
+      </c>
+      <c r="Q58">
+        <v>-3.710549200000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1849640806416413</v>
+      </c>
+      <c r="T58">
+        <v>1.588646298568318</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.1068061696886418</v>
+      </c>
+      <c r="W58">
+        <v>0.2132946866783523</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4272246787545673</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2028292200221995</v>
+      </c>
+      <c r="C59">
+        <v>-2.686198834615702</v>
+      </c>
+      <c r="D59">
+        <v>22.9778011653843</v>
+      </c>
+      <c r="E59">
+        <v>16.66400000000001</v>
+      </c>
+      <c r="F59">
+        <v>37.16400000000001</v>
+      </c>
+      <c r="G59">
+        <v>11.5</v>
+      </c>
+      <c r="H59">
+        <v>44.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.76</v>
+      </c>
+      <c r="K59">
+        <v>0.035</v>
+      </c>
+      <c r="L59">
+        <v>3.725</v>
+      </c>
+      <c r="M59">
+        <v>8.874763200000002</v>
+      </c>
+      <c r="N59">
+        <v>-5.149763200000002</v>
+      </c>
+      <c r="O59">
+        <v>-1.287440800000001</v>
+      </c>
+      <c r="P59">
+        <v>-3.862322400000002</v>
+      </c>
+      <c r="Q59">
+        <v>-3.827322400000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.188363245307726</v>
+      </c>
+      <c r="T59">
+        <v>1.625591561325721</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.1049323772379639</v>
+      </c>
+      <c r="W59">
+        <v>0.2137421483155742</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4197295089518556</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2048292200221995</v>
+      </c>
+      <c r="C60">
+        <v>-3.614991090368179</v>
+      </c>
+      <c r="D60">
+        <v>22.70100890963183</v>
+      </c>
+      <c r="E60">
+        <v>17.316</v>
+      </c>
+      <c r="F60">
+        <v>37.816</v>
+      </c>
+      <c r="G60">
+        <v>11.5</v>
+      </c>
+      <c r="H60">
+        <v>44.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.76</v>
+      </c>
+      <c r="K60">
+        <v>0.035</v>
+      </c>
+      <c r="L60">
+        <v>3.725</v>
+      </c>
+      <c r="M60">
+        <v>9.0304608</v>
+      </c>
+      <c r="N60">
+        <v>-5.305460800000001</v>
+      </c>
+      <c r="O60">
+        <v>-1.3263652</v>
+      </c>
+      <c r="P60">
+        <v>-3.9790956</v>
+      </c>
+      <c r="Q60">
+        <v>-3.9440956</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.19192427495791</v>
+      </c>
+      <c r="T60">
+        <v>1.664296122309667</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.103123198320068</v>
+      </c>
+      <c r="W60">
+        <v>0.2141741802411678</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.412492793280272</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2068292200221995</v>
+      </c>
+      <c r="C61">
+        <v>-4.537194200358591</v>
+      </c>
+      <c r="D61">
+        <v>22.4308057996414</v>
+      </c>
+      <c r="E61">
+        <v>17.968</v>
+      </c>
+      <c r="F61">
+        <v>38.468</v>
+      </c>
+      <c r="G61">
+        <v>11.5</v>
+      </c>
+      <c r="H61">
+        <v>44.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.76</v>
+      </c>
+      <c r="K61">
+        <v>0.035</v>
+      </c>
+      <c r="L61">
+        <v>3.725</v>
+      </c>
+      <c r="M61">
+        <v>9.1861584</v>
+      </c>
+      <c r="N61">
+        <v>-5.4611584</v>
+      </c>
+      <c r="O61">
+        <v>-1.3652896</v>
+      </c>
+      <c r="P61">
+        <v>-4.0958688</v>
+      </c>
+      <c r="Q61">
+        <v>-4.0608688</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1956590133715175</v>
+      </c>
+      <c r="T61">
+        <v>1.704888710658683</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.1013753475010838</v>
+      </c>
+      <c r="W61">
+        <v>0.2145915670167412</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4055013900043352</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2088292200221995</v>
+      </c>
+      <c r="C62">
+        <v>-5.453040682706899</v>
+      </c>
+      <c r="D62">
+        <v>22.1669593172931</v>
+      </c>
+      <c r="E62">
+        <v>18.62</v>
+      </c>
+      <c r="F62">
+        <v>39.12</v>
+      </c>
+      <c r="G62">
+        <v>11.5</v>
+      </c>
+      <c r="H62">
+        <v>44.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.76</v>
+      </c>
+      <c r="K62">
+        <v>0.035</v>
+      </c>
+      <c r="L62">
+        <v>3.725</v>
+      </c>
+      <c r="M62">
+        <v>9.341856</v>
+      </c>
+      <c r="N62">
+        <v>-5.616856</v>
+      </c>
+      <c r="O62">
+        <v>-1.404214</v>
+      </c>
+      <c r="P62">
+        <v>-4.212642000000001</v>
+      </c>
+      <c r="Q62">
+        <v>-4.177642000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1995804887058055</v>
+      </c>
+      <c r="T62">
+        <v>1.74751092842515</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09968575837606573</v>
+      </c>
+      <c r="W62">
+        <v>0.2149950408997955</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3987430335042629</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2108292200221995</v>
+      </c>
+      <c r="C63">
+        <v>-6.362752242573677</v>
+      </c>
+      <c r="D63">
+        <v>21.90924775742632</v>
+      </c>
+      <c r="E63">
+        <v>19.272</v>
+      </c>
+      <c r="F63">
+        <v>39.772</v>
+      </c>
+      <c r="G63">
+        <v>11.5</v>
+      </c>
+      <c r="H63">
+        <v>44.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.76</v>
+      </c>
+      <c r="K63">
+        <v>0.035</v>
+      </c>
+      <c r="L63">
+        <v>3.725</v>
+      </c>
+      <c r="M63">
+        <v>9.4975536</v>
+      </c>
+      <c r="N63">
+        <v>-5.7725536</v>
+      </c>
+      <c r="O63">
+        <v>-1.4431384</v>
+      </c>
+      <c r="P63">
+        <v>-4.3294152</v>
+      </c>
+      <c r="Q63">
+        <v>-4.2944152</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2037030653392876</v>
+      </c>
+      <c r="T63">
+        <v>1.792318900948872</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.09805156561580236</v>
+      </c>
+      <c r="W63">
+        <v>0.2153852861309464</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3922062624632094</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2128292200221995</v>
+      </c>
+      <c r="C64">
+        <v>-7.26654039349031</v>
+      </c>
+      <c r="D64">
+        <v>21.65745960650969</v>
+      </c>
+      <c r="E64">
+        <v>19.924</v>
+      </c>
+      <c r="F64">
+        <v>40.424</v>
+      </c>
+      <c r="G64">
+        <v>11.5</v>
+      </c>
+      <c r="H64">
+        <v>44.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.76</v>
+      </c>
+      <c r="K64">
+        <v>0.035</v>
+      </c>
+      <c r="L64">
+        <v>3.725</v>
+      </c>
+      <c r="M64">
+        <v>9.6532512</v>
+      </c>
+      <c r="N64">
+        <v>-5.9282512</v>
+      </c>
+      <c r="O64">
+        <v>-1.4820628</v>
+      </c>
+      <c r="P64">
+        <v>-4.4461884</v>
+      </c>
+      <c r="Q64">
+        <v>-4.4111884</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2080426196903216</v>
+      </c>
+      <c r="T64">
+        <v>1.839485187815948</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09647008875103136</v>
+      </c>
+      <c r="W64">
+        <v>0.2157629428062537</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3858803550041254</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2148292200221995</v>
+      </c>
+      <c r="C65">
+        <v>-8.164607036332647</v>
+      </c>
+      <c r="D65">
+        <v>21.41139296366735</v>
+      </c>
+      <c r="E65">
+        <v>20.576</v>
+      </c>
+      <c r="F65">
+        <v>41.076</v>
+      </c>
+      <c r="G65">
+        <v>11.5</v>
+      </c>
+      <c r="H65">
+        <v>44.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.76</v>
+      </c>
+      <c r="K65">
+        <v>0.035</v>
+      </c>
+      <c r="L65">
+        <v>3.725</v>
+      </c>
+      <c r="M65">
+        <v>9.808948800000001</v>
+      </c>
+      <c r="N65">
+        <v>-6.083948800000002</v>
+      </c>
+      <c r="O65">
+        <v>-1.5209872</v>
+      </c>
+      <c r="P65">
+        <v>-4.562961600000001</v>
+      </c>
+      <c r="Q65">
+        <v>-4.527961600000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2126167445468167</v>
+      </c>
+      <c r="T65">
+        <v>1.889201003702865</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.09493881750101497</v>
+      </c>
+      <c r="W65">
+        <v>0.2161286103807576</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3797552700040598</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2168292200221995</v>
+      </c>
+      <c r="C66">
+        <v>-9.057144999269276</v>
+      </c>
+      <c r="D66">
+        <v>21.17085500073073</v>
+      </c>
+      <c r="E66">
+        <v>21.228</v>
+      </c>
+      <c r="F66">
+        <v>41.728</v>
+      </c>
+      <c r="G66">
+        <v>11.5</v>
+      </c>
+      <c r="H66">
+        <v>44.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.76</v>
+      </c>
+      <c r="K66">
+        <v>0.035</v>
+      </c>
+      <c r="L66">
+        <v>3.725</v>
+      </c>
+      <c r="M66">
+        <v>9.964646400000001</v>
+      </c>
+      <c r="N66">
+        <v>-6.239646400000002</v>
+      </c>
+      <c r="O66">
+        <v>-1.5599116</v>
+      </c>
+      <c r="P66">
+        <v>-4.679734800000001</v>
+      </c>
+      <c r="Q66">
+        <v>-4.644734800000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.217444987450895</v>
+      </c>
+      <c r="T66">
+        <v>1.941678809361278</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.09345539847756161</v>
+      </c>
+      <c r="W66">
+        <v>0.2164828508435583</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3738215939102465</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2188292200221995</v>
+      </c>
+      <c r="C67">
+        <v>-9.944338541718885</v>
+      </c>
+      <c r="D67">
+        <v>20.93566145828112</v>
+      </c>
+      <c r="E67">
+        <v>21.88</v>
+      </c>
+      <c r="F67">
+        <v>42.38</v>
+      </c>
+      <c r="G67">
+        <v>11.5</v>
+      </c>
+      <c r="H67">
+        <v>44.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.76</v>
+      </c>
+      <c r="K67">
+        <v>0.035</v>
+      </c>
+      <c r="L67">
+        <v>3.725</v>
+      </c>
+      <c r="M67">
+        <v>10.120344</v>
+      </c>
+      <c r="N67">
+        <v>-6.395344000000001</v>
+      </c>
+      <c r="O67">
+        <v>-1.598836</v>
+      </c>
+      <c r="P67">
+        <v>-4.796508000000001</v>
+      </c>
+      <c r="Q67">
+        <v>-4.761508000000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.222549129949492</v>
+      </c>
+      <c r="T67">
+        <v>1.997155346771601</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.09201762311636835</v>
+      </c>
+      <c r="W67">
+        <v>0.2168261915998113</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3680704924654734</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2208292200221995</v>
+      </c>
+      <c r="C68">
+        <v>-10.82636382508523</v>
+      </c>
+      <c r="D68">
+        <v>20.70563617491477</v>
+      </c>
+      <c r="E68">
+        <v>22.532</v>
+      </c>
+      <c r="F68">
+        <v>43.032</v>
+      </c>
+      <c r="G68">
+        <v>11.5</v>
+      </c>
+      <c r="H68">
+        <v>44.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.76</v>
+      </c>
+      <c r="K68">
+        <v>0.035</v>
+      </c>
+      <c r="L68">
+        <v>3.725</v>
+      </c>
+      <c r="M68">
+        <v>10.2760416</v>
+      </c>
+      <c r="N68">
+        <v>-6.551041600000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.6377604</v>
+      </c>
+      <c r="P68">
+        <v>-4.913281200000001</v>
+      </c>
+      <c r="Q68">
+        <v>-4.878281200000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.227953516124477</v>
+      </c>
+      <c r="T68">
+        <v>2.055895209911942</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0906234167055143</v>
+      </c>
+      <c r="W68">
+        <v>0.2171591280907232</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3624936668220572</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2228292200221995</v>
+      </c>
+      <c r="C69">
+        <v>-11.70338935279673</v>
+      </c>
+      <c r="D69">
+        <v>20.48061064720327</v>
+      </c>
+      <c r="E69">
+        <v>23.184</v>
+      </c>
+      <c r="F69">
+        <v>43.684</v>
+      </c>
+      <c r="G69">
+        <v>11.5</v>
+      </c>
+      <c r="H69">
+        <v>44.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.76</v>
+      </c>
+      <c r="K69">
+        <v>0.035</v>
+      </c>
+      <c r="L69">
+        <v>3.725</v>
+      </c>
+      <c r="M69">
+        <v>10.4317392</v>
+      </c>
+      <c r="N69">
+        <v>-6.706739200000001</v>
+      </c>
+      <c r="O69">
+        <v>-1.6766848</v>
+      </c>
+      <c r="P69">
+        <v>-5.030054400000001</v>
+      </c>
+      <c r="Q69">
+        <v>-4.995054400000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2336854408555218</v>
+      </c>
+      <c r="T69">
+        <v>2.118195064757758</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08927082839647676</v>
+      </c>
+      <c r="W69">
+        <v>0.2174821261789214</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3570833135859071</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2248292200221995</v>
+      </c>
+      <c r="C70">
+        <v>-12.57557638196085</v>
+      </c>
+      <c r="D70">
+        <v>20.26042361803916</v>
+      </c>
+      <c r="E70">
+        <v>23.83600000000001</v>
+      </c>
+      <c r="F70">
+        <v>44.33600000000001</v>
+      </c>
+      <c r="G70">
+        <v>11.5</v>
+      </c>
+      <c r="H70">
+        <v>44.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.76</v>
+      </c>
+      <c r="K70">
+        <v>0.035</v>
+      </c>
+      <c r="L70">
+        <v>3.725</v>
+      </c>
+      <c r="M70">
+        <v>10.5874368</v>
+      </c>
+      <c r="N70">
+        <v>-6.862436800000003</v>
+      </c>
+      <c r="O70">
+        <v>-1.715609200000001</v>
+      </c>
+      <c r="P70">
+        <v>-5.146827600000002</v>
+      </c>
+      <c r="Q70">
+        <v>-5.111827600000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2397756108822569</v>
+      </c>
+      <c r="T70">
+        <v>2.184388660531438</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08795802209652856</v>
+      </c>
+      <c r="W70">
+        <v>0.217795624323349</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3518320883861142</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2268292200221995</v>
+      </c>
+      <c r="C71">
+        <v>-13.44307930874688</v>
+      </c>
+      <c r="D71">
+        <v>20.04492069125313</v>
+      </c>
+      <c r="E71">
+        <v>24.48800000000001</v>
+      </c>
+      <c r="F71">
+        <v>44.98800000000001</v>
+      </c>
+      <c r="G71">
+        <v>11.5</v>
+      </c>
+      <c r="H71">
+        <v>44.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.76</v>
+      </c>
+      <c r="K71">
+        <v>0.035</v>
+      </c>
+      <c r="L71">
+        <v>3.725</v>
+      </c>
+      <c r="M71">
+        <v>10.7431344</v>
+      </c>
+      <c r="N71">
+        <v>-7.018134400000003</v>
+      </c>
+      <c r="O71">
+        <v>-1.754533600000001</v>
+      </c>
+      <c r="P71">
+        <v>-5.263600800000003</v>
+      </c>
+      <c r="Q71">
+        <v>-5.228600800000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2462586951042652</v>
+      </c>
+      <c r="T71">
+        <v>2.254852810871162</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.08668326815310062</v>
+      </c>
+      <c r="W71">
+        <v>0.2181000355650396</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3467330726124025</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2288292200221995</v>
+      </c>
+      <c r="C72">
+        <v>-14.30604602943238</v>
+      </c>
+      <c r="D72">
+        <v>19.83395397056763</v>
+      </c>
+      <c r="E72">
+        <v>25.14000000000001</v>
+      </c>
+      <c r="F72">
+        <v>45.64000000000001</v>
+      </c>
+      <c r="G72">
+        <v>11.5</v>
+      </c>
+      <c r="H72">
+        <v>44.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.76</v>
+      </c>
+      <c r="K72">
+        <v>0.035</v>
+      </c>
+      <c r="L72">
+        <v>3.725</v>
+      </c>
+      <c r="M72">
+        <v>10.898832</v>
+      </c>
+      <c r="N72">
+        <v>-7.173832000000003</v>
+      </c>
+      <c r="O72">
+        <v>-1.793458000000001</v>
+      </c>
+      <c r="P72">
+        <v>-5.380374000000002</v>
+      </c>
+      <c r="Q72">
+        <v>-5.345374000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.253173984941074</v>
+      </c>
+      <c r="T72">
+        <v>2.330014571233534</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.08544493575091347</v>
+      </c>
+      <c r="W72">
+        <v>0.2183957493426819</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3417797430036539</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2308292200221995</v>
+      </c>
+      <c r="C73">
+        <v>-15.16461827888768</v>
+      </c>
+      <c r="D73">
+        <v>19.62738172111232</v>
+      </c>
+      <c r="E73">
+        <v>25.792</v>
+      </c>
+      <c r="F73">
+        <v>46.292</v>
+      </c>
+      <c r="G73">
+        <v>11.5</v>
+      </c>
+      <c r="H73">
+        <v>44.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.76</v>
+      </c>
+      <c r="K73">
+        <v>0.035</v>
+      </c>
+      <c r="L73">
+        <v>3.725</v>
+      </c>
+      <c r="M73">
+        <v>11.0545296</v>
+      </c>
+      <c r="N73">
+        <v>-7.329529600000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.8323824</v>
+      </c>
+      <c r="P73">
+        <v>-5.497147200000001</v>
+      </c>
+      <c r="Q73">
+        <v>-5.4621472</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2605661913183523</v>
+      </c>
+      <c r="T73">
+        <v>2.410359901276069</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.08424148595160484</v>
+      </c>
+      <c r="W73">
+        <v>0.2186831331547568</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3369659438064193</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2328292200221995</v>
+      </c>
+      <c r="C74">
+        <v>-16.01893194812645</v>
+      </c>
+      <c r="D74">
+        <v>19.42506805187356</v>
+      </c>
+      <c r="E74">
+        <v>26.444</v>
+      </c>
+      <c r="F74">
+        <v>46.944</v>
+      </c>
+      <c r="G74">
+        <v>11.5</v>
+      </c>
+      <c r="H74">
+        <v>44.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.76</v>
+      </c>
+      <c r="K74">
+        <v>0.035</v>
+      </c>
+      <c r="L74">
+        <v>3.725</v>
+      </c>
+      <c r="M74">
+        <v>11.2102272</v>
+      </c>
+      <c r="N74">
+        <v>-7.485227200000002</v>
+      </c>
+      <c r="O74">
+        <v>-1.871306800000001</v>
+      </c>
+      <c r="P74">
+        <v>-5.613920400000001</v>
+      </c>
+      <c r="Q74">
+        <v>-5.578920400000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.268486412436865</v>
+      </c>
+      <c r="T74">
+        <v>2.4964441834645</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08307146531338809</v>
+      </c>
+      <c r="W74">
+        <v>0.2189625340831629</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3322858612535524</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2348292200221995</v>
+      </c>
+      <c r="C75">
+        <v>-16.86911738241704</v>
+      </c>
+      <c r="D75">
+        <v>19.22688261758296</v>
+      </c>
+      <c r="E75">
+        <v>27.096</v>
+      </c>
+      <c r="F75">
+        <v>47.596</v>
+      </c>
+      <c r="G75">
+        <v>11.5</v>
+      </c>
+      <c r="H75">
+        <v>44.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.76</v>
+      </c>
+      <c r="K75">
+        <v>0.035</v>
+      </c>
+      <c r="L75">
+        <v>3.725</v>
+      </c>
+      <c r="M75">
+        <v>11.3659248</v>
+      </c>
+      <c r="N75">
+        <v>-7.640924800000002</v>
+      </c>
+      <c r="O75">
+        <v>-1.910231200000001</v>
+      </c>
+      <c r="P75">
+        <v>-5.730693600000002</v>
+      </c>
+      <c r="Q75">
+        <v>-5.695693600000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2769933166011933</v>
+      </c>
+      <c r="T75">
+        <v>2.588905079148371</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.08193350003512251</v>
+      </c>
+      <c r="W75">
+        <v>0.2192342801916128</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.32773400014049</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2368292200221995</v>
+      </c>
+      <c r="C76">
+        <v>-17.71529966132949</v>
+      </c>
+      <c r="D76">
+        <v>19.03270033867051</v>
+      </c>
+      <c r="E76">
+        <v>27.748</v>
+      </c>
+      <c r="F76">
+        <v>48.248</v>
+      </c>
+      <c r="G76">
+        <v>11.5</v>
+      </c>
+      <c r="H76">
+        <v>44.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.76</v>
+      </c>
+      <c r="K76">
+        <v>0.035</v>
+      </c>
+      <c r="L76">
+        <v>3.725</v>
+      </c>
+      <c r="M76">
+        <v>11.5216224</v>
+      </c>
+      <c r="N76">
+        <v>-7.796622400000002</v>
+      </c>
+      <c r="O76">
+        <v>-1.949155600000001</v>
+      </c>
+      <c r="P76">
+        <v>-5.847466800000001</v>
+      </c>
+      <c r="Q76">
+        <v>-5.812466800000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2861545980089314</v>
+      </c>
+      <c r="T76">
+        <v>2.688478351423308</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08082629057518842</v>
+      </c>
+      <c r="W76">
+        <v>0.219498681810645</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3233051623007537</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2388292200221995</v>
+      </c>
+      <c r="C77">
+        <v>-18.55759886198186</v>
+      </c>
+      <c r="D77">
+        <v>18.84240113801814</v>
+      </c>
+      <c r="E77">
+        <v>28.40000000000001</v>
+      </c>
+      <c r="F77">
+        <v>48.90000000000001</v>
+      </c>
+      <c r="G77">
+        <v>11.5</v>
+      </c>
+      <c r="H77">
+        <v>44.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.76</v>
+      </c>
+      <c r="K77">
+        <v>0.035</v>
+      </c>
+      <c r="L77">
+        <v>3.725</v>
+      </c>
+      <c r="M77">
+        <v>11.67732</v>
+      </c>
+      <c r="N77">
+        <v>-7.952320000000002</v>
+      </c>
+      <c r="O77">
+        <v>-1.988080000000001</v>
+      </c>
+      <c r="P77">
+        <v>-5.964240000000002</v>
+      </c>
+      <c r="Q77">
+        <v>-5.929240000000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2960487819292887</v>
+      </c>
+      <c r="T77">
+        <v>2.79601748548024</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07974860670085257</v>
+      </c>
+      <c r="W77">
+        <v>0.2197560327198364</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3189944268034103</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2408292200221995</v>
+      </c>
+      <c r="C78">
+        <v>-19.39613030665058</v>
+      </c>
+      <c r="D78">
+        <v>18.65586969334942</v>
+      </c>
+      <c r="E78">
+        <v>29.052</v>
+      </c>
+      <c r="F78">
+        <v>49.552</v>
+      </c>
+      <c r="G78">
+        <v>11.5</v>
+      </c>
+      <c r="H78">
+        <v>44.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.76</v>
+      </c>
+      <c r="K78">
+        <v>0.035</v>
+      </c>
+      <c r="L78">
+        <v>3.725</v>
+      </c>
+      <c r="M78">
+        <v>11.8330176</v>
+      </c>
+      <c r="N78">
+        <v>-8.1080176</v>
+      </c>
+      <c r="O78">
+        <v>-2.0270044</v>
+      </c>
+      <c r="P78">
+        <v>-6.0810132</v>
+      </c>
+      <c r="Q78">
+        <v>-6.0460132</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3067674811763424</v>
+      </c>
+      <c r="T78">
+        <v>2.912518214041917</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07869928292847295</v>
+      </c>
+      <c r="W78">
+        <v>0.2200066112366807</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3147971317138918</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2428292200221995</v>
+      </c>
+      <c r="C79">
+        <v>-20.23100479581757</v>
+      </c>
+      <c r="D79">
+        <v>18.47299520418243</v>
+      </c>
+      <c r="E79">
+        <v>29.704</v>
+      </c>
+      <c r="F79">
+        <v>50.204</v>
+      </c>
+      <c r="G79">
+        <v>11.5</v>
+      </c>
+      <c r="H79">
+        <v>44.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.76</v>
+      </c>
+      <c r="K79">
+        <v>0.035</v>
+      </c>
+      <c r="L79">
+        <v>3.725</v>
+      </c>
+      <c r="M79">
+        <v>11.9887152</v>
+      </c>
+      <c r="N79">
+        <v>-8.263715200000002</v>
+      </c>
+      <c r="O79">
+        <v>-2.0659288</v>
+      </c>
+      <c r="P79">
+        <v>-6.197786400000002</v>
+      </c>
+      <c r="Q79">
+        <v>-6.162786400000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3184182412274878</v>
+      </c>
+      <c r="T79">
+        <v>3.039149440739392</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07767721431901226</v>
+      </c>
+      <c r="W79">
+        <v>0.2202506812206199</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.310708857276049</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2448292200221995</v>
+      </c>
+      <c r="C80">
+        <v>-21.06232882764366</v>
+      </c>
+      <c r="D80">
+        <v>18.29367117235634</v>
+      </c>
+      <c r="E80">
+        <v>30.356</v>
+      </c>
+      <c r="F80">
+        <v>50.856</v>
+      </c>
+      <c r="G80">
+        <v>11.5</v>
+      </c>
+      <c r="H80">
+        <v>44.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.76</v>
+      </c>
+      <c r="K80">
+        <v>0.035</v>
+      </c>
+      <c r="L80">
+        <v>3.725</v>
+      </c>
+      <c r="M80">
+        <v>12.1444128</v>
+      </c>
+      <c r="N80">
+        <v>-8.419412800000002</v>
+      </c>
+      <c r="O80">
+        <v>-2.1048532</v>
+      </c>
+      <c r="P80">
+        <v>-6.314559600000001</v>
+      </c>
+      <c r="Q80">
+        <v>-6.279559600000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3311281612832827</v>
+      </c>
+      <c r="T80">
+        <v>3.177292597136637</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07668135259697363</v>
+      </c>
+      <c r="W80">
+        <v>0.2204884929998427</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3067254103878945</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2468292200221995</v>
+      </c>
+      <c r="C81">
+        <v>-21.89020480478191</v>
+      </c>
+      <c r="D81">
+        <v>18.1177951952181</v>
+      </c>
+      <c r="E81">
+        <v>31.008</v>
+      </c>
+      <c r="F81">
+        <v>51.508</v>
+      </c>
+      <c r="G81">
+        <v>11.5</v>
+      </c>
+      <c r="H81">
+        <v>44.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.76</v>
+      </c>
+      <c r="K81">
+        <v>0.035</v>
+      </c>
+      <c r="L81">
+        <v>3.725</v>
+      </c>
+      <c r="M81">
+        <v>12.3001104</v>
+      </c>
+      <c r="N81">
+        <v>-8.575110400000002</v>
+      </c>
+      <c r="O81">
+        <v>-2.1437776</v>
+      </c>
+      <c r="P81">
+        <v>-6.431332800000002</v>
+      </c>
+      <c r="Q81">
+        <v>-6.396332800000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.34504854991582</v>
+      </c>
+      <c r="T81">
+        <v>3.328592244619334</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07571070256410055</v>
+      </c>
+      <c r="W81">
+        <v>0.2207202842276928</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3028428102564021</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2488292200221995</v>
+      </c>
+      <c r="C82">
+        <v>-22.71473122937467</v>
+      </c>
+      <c r="D82">
+        <v>17.94526877062533</v>
+      </c>
+      <c r="E82">
+        <v>31.66</v>
+      </c>
+      <c r="F82">
+        <v>52.16</v>
+      </c>
+      <c r="G82">
+        <v>11.5</v>
+      </c>
+      <c r="H82">
+        <v>44.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.76</v>
+      </c>
+      <c r="K82">
+        <v>0.035</v>
+      </c>
+      <c r="L82">
+        <v>3.725</v>
+      </c>
+      <c r="M82">
+        <v>12.455808</v>
+      </c>
+      <c r="N82">
+        <v>-8.730808000000001</v>
+      </c>
+      <c r="O82">
+        <v>-2.182702</v>
+      </c>
+      <c r="P82">
+        <v>-6.548106000000001</v>
+      </c>
+      <c r="Q82">
+        <v>-6.513106000000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.360360977411611</v>
+      </c>
+      <c r="T82">
+        <v>3.495021856850301</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0747643187820493</v>
+      </c>
+      <c r="W82">
+        <v>0.2209462806748466</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2990572751281971</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2508292200221995</v>
+      </c>
+      <c r="C83">
+        <v>-23.53600288701456</v>
+      </c>
+      <c r="D83">
+        <v>17.77599711298545</v>
+      </c>
+      <c r="E83">
+        <v>32.312</v>
+      </c>
+      <c r="F83">
+        <v>52.812</v>
+      </c>
+      <c r="G83">
+        <v>11.5</v>
+      </c>
+      <c r="H83">
+        <v>44.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.76</v>
+      </c>
+      <c r="K83">
+        <v>0.035</v>
+      </c>
+      <c r="L83">
+        <v>3.725</v>
+      </c>
+      <c r="M83">
+        <v>12.6115056</v>
+      </c>
+      <c r="N83">
+        <v>-8.886505600000001</v>
+      </c>
+      <c r="O83">
+        <v>-2.2216264</v>
+      </c>
+      <c r="P83">
+        <v>-6.664879200000001</v>
+      </c>
+      <c r="Q83">
+        <v>-6.629879200000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3772852393806431</v>
+      </c>
+      <c r="T83">
+        <v>3.678970375631895</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07384130250078942</v>
+      </c>
+      <c r="W83">
+        <v>0.2211666969628115</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2953652100031577</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2528292200221995</v>
+      </c>
+      <c r="C84">
+        <v>-24.35411102039131</v>
+      </c>
+      <c r="D84">
+        <v>17.60988897960869</v>
+      </c>
+      <c r="E84">
+        <v>32.96400000000001</v>
+      </c>
+      <c r="F84">
+        <v>53.46400000000001</v>
+      </c>
+      <c r="G84">
+        <v>11.5</v>
+      </c>
+      <c r="H84">
+        <v>44.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.76</v>
+      </c>
+      <c r="K84">
+        <v>0.035</v>
+      </c>
+      <c r="L84">
+        <v>3.725</v>
+      </c>
+      <c r="M84">
+        <v>12.7672032</v>
+      </c>
+      <c r="N84">
+        <v>-9.042203200000003</v>
+      </c>
+      <c r="O84">
+        <v>-2.260550800000001</v>
+      </c>
+      <c r="P84">
+        <v>-6.781652400000002</v>
+      </c>
+      <c r="Q84">
+        <v>-6.746652400000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.39608997490179</v>
+      </c>
+      <c r="T84">
+        <v>3.883357618722557</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0729407988117554</v>
+      </c>
+      <c r="W84">
+        <v>0.2213817372437528</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2917631952470215</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2548292200221995</v>
+      </c>
+      <c r="C85">
+        <v>-25.1691434932929</v>
+      </c>
+      <c r="D85">
+        <v>17.44685650670711</v>
+      </c>
+      <c r="E85">
+        <v>33.61600000000001</v>
+      </c>
+      <c r="F85">
+        <v>54.11600000000001</v>
+      </c>
+      <c r="G85">
+        <v>11.5</v>
+      </c>
+      <c r="H85">
+        <v>44.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.76</v>
+      </c>
+      <c r="K85">
+        <v>0.035</v>
+      </c>
+      <c r="L85">
+        <v>3.725</v>
+      </c>
+      <c r="M85">
+        <v>12.9229008</v>
+      </c>
+      <c r="N85">
+        <v>-9.197900800000003</v>
+      </c>
+      <c r="O85">
+        <v>-2.299475200000001</v>
+      </c>
+      <c r="P85">
+        <v>-6.898425600000002</v>
+      </c>
+      <c r="Q85">
+        <v>-6.863425600000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4171070322489542</v>
+      </c>
+      <c r="T85">
+        <v>4.111790419823884</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07206199400679449</v>
+      </c>
+      <c r="W85">
+        <v>0.2215915958311775</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.288247976027178</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2568292200221995</v>
+      </c>
+      <c r="C86">
+        <v>-25.98118494558016</v>
+      </c>
+      <c r="D86">
+        <v>17.28681505441984</v>
+      </c>
+      <c r="E86">
+        <v>34.268</v>
+      </c>
+      <c r="F86">
+        <v>54.768</v>
+      </c>
+      <c r="G86">
+        <v>11.5</v>
+      </c>
+      <c r="H86">
+        <v>44.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.76</v>
+      </c>
+      <c r="K86">
+        <v>0.035</v>
+      </c>
+      <c r="L86">
+        <v>3.725</v>
+      </c>
+      <c r="M86">
+        <v>13.0785984</v>
+      </c>
+      <c r="N86">
+        <v>-9.353598400000001</v>
+      </c>
+      <c r="O86">
+        <v>-2.3383996</v>
+      </c>
+      <c r="P86">
+        <v>-7.0151988</v>
+      </c>
+      <c r="Q86">
+        <v>-6.9801988</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4407512217645136</v>
+      </c>
+      <c r="T86">
+        <v>4.368777321062875</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07120411312576123</v>
+      </c>
+      <c r="W86">
+        <v>0.2217964577855682</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2848164525030449</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2588292200221995</v>
+      </c>
+      <c r="C87">
+        <v>-26.79031693970963</v>
+      </c>
+      <c r="D87">
+        <v>17.12968306029037</v>
+      </c>
+      <c r="E87">
+        <v>34.92</v>
+      </c>
+      <c r="F87">
+        <v>55.42</v>
+      </c>
+      <c r="G87">
+        <v>11.5</v>
+      </c>
+      <c r="H87">
+        <v>44.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.76</v>
+      </c>
+      <c r="K87">
+        <v>0.035</v>
+      </c>
+      <c r="L87">
+        <v>3.725</v>
+      </c>
+      <c r="M87">
+        <v>13.234296</v>
+      </c>
+      <c r="N87">
+        <v>-9.509296000000001</v>
+      </c>
+      <c r="O87">
+        <v>-2.377324</v>
+      </c>
+      <c r="P87">
+        <v>-7.131972000000001</v>
+      </c>
+      <c r="Q87">
+        <v>-7.096972000000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4675479698821478</v>
+      </c>
+      <c r="T87">
+        <v>4.660029142467066</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07036641767722286</v>
+      </c>
+      <c r="W87">
+        <v>0.2219964994586792</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2814656707088915</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2608292200221995</v>
+      </c>
+      <c r="C88">
+        <v>-27.59661809933698</v>
+      </c>
+      <c r="D88">
+        <v>16.97538190066302</v>
+      </c>
+      <c r="E88">
+        <v>35.572</v>
+      </c>
+      <c r="F88">
+        <v>56.072</v>
+      </c>
+      <c r="G88">
+        <v>11.5</v>
+      </c>
+      <c r="H88">
+        <v>44.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.76</v>
+      </c>
+      <c r="K88">
+        <v>0.035</v>
+      </c>
+      <c r="L88">
+        <v>3.725</v>
+      </c>
+      <c r="M88">
+        <v>13.3899936</v>
+      </c>
+      <c r="N88">
+        <v>-9.664993600000003</v>
+      </c>
+      <c r="O88">
+        <v>-2.416248400000001</v>
+      </c>
+      <c r="P88">
+        <v>-7.248745200000002</v>
+      </c>
+      <c r="Q88">
+        <v>-7.213745200000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4981728248737299</v>
+      </c>
+      <c r="T88">
+        <v>4.992888366929001</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06954820351818539</v>
+      </c>
+      <c r="W88">
+        <v>0.2221918889998573</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2781928140727415</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2628292200221995</v>
+      </c>
+      <c r="C89">
+        <v>-28.40016424049643</v>
+      </c>
+      <c r="D89">
+        <v>16.82383575950357</v>
+      </c>
+      <c r="E89">
+        <v>36.224</v>
+      </c>
+      <c r="F89">
+        <v>56.724</v>
+      </c>
+      <c r="G89">
+        <v>11.5</v>
+      </c>
+      <c r="H89">
+        <v>44.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.76</v>
+      </c>
+      <c r="K89">
+        <v>0.035</v>
+      </c>
+      <c r="L89">
+        <v>3.725</v>
+      </c>
+      <c r="M89">
+        <v>13.5456912</v>
+      </c>
+      <c r="N89">
+        <v>-9.820691200000002</v>
+      </c>
+      <c r="O89">
+        <v>-2.455172800000001</v>
+      </c>
+      <c r="P89">
+        <v>-7.365518400000002</v>
+      </c>
+      <c r="Q89">
+        <v>-7.330518400000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5335091960178628</v>
+      </c>
+      <c r="T89">
+        <v>5.376956702846615</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06874879888004533</v>
+      </c>
+      <c r="W89">
+        <v>0.2223827868274452</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2749951955201813</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2648292200221996</v>
+      </c>
+      <c r="C90">
+        <v>-29.20102849581574</v>
+      </c>
+      <c r="D90">
+        <v>16.67497150418427</v>
+      </c>
+      <c r="E90">
+        <v>36.876</v>
+      </c>
+      <c r="F90">
+        <v>57.376</v>
+      </c>
+      <c r="G90">
+        <v>11.5</v>
+      </c>
+      <c r="H90">
+        <v>44.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.76</v>
+      </c>
+      <c r="K90">
+        <v>0.035</v>
+      </c>
+      <c r="L90">
+        <v>3.725</v>
+      </c>
+      <c r="M90">
+        <v>13.7013888</v>
+      </c>
+      <c r="N90">
+        <v>-9.976388800000002</v>
+      </c>
+      <c r="O90">
+        <v>-2.494097200000001</v>
+      </c>
+      <c r="P90">
+        <v>-7.482291600000002</v>
+      </c>
+      <c r="Q90">
+        <v>-7.447291600000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.574734962352685</v>
+      </c>
+      <c r="T90">
+        <v>5.825036428083834</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06796756252913572</v>
+      </c>
+      <c r="W90">
+        <v>0.2225693460680424</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2718702501165429</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2668292200221994</v>
+      </c>
+      <c r="C91">
+        <v>-29.99928143219433</v>
+      </c>
+      <c r="D91">
+        <v>16.52871856780568</v>
+      </c>
+      <c r="E91">
+        <v>37.52800000000001</v>
+      </c>
+      <c r="F91">
+        <v>58.02800000000001</v>
+      </c>
+      <c r="G91">
+        <v>11.5</v>
+      </c>
+      <c r="H91">
+        <v>44.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.76</v>
+      </c>
+      <c r="K91">
+        <v>0.035</v>
+      </c>
+      <c r="L91">
+        <v>3.725</v>
+      </c>
+      <c r="M91">
+        <v>13.8570864</v>
+      </c>
+      <c r="N91">
+        <v>-10.1320864</v>
+      </c>
+      <c r="O91">
+        <v>-2.533021600000001</v>
+      </c>
+      <c r="P91">
+        <v>-7.599064800000002</v>
+      </c>
+      <c r="Q91">
+        <v>-7.564064800000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6234563225665652</v>
+      </c>
+      <c r="T91">
+        <v>6.354585194273273</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06720388205128026</v>
+      </c>
+      <c r="W91">
+        <v>0.2227517129661543</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.268815528205121</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2688292200221996</v>
+      </c>
+      <c r="C92">
+        <v>-30.79499116234263</v>
+      </c>
+      <c r="D92">
+        <v>16.38500883765738</v>
+      </c>
+      <c r="E92">
+        <v>38.18000000000001</v>
+      </c>
+      <c r="F92">
+        <v>58.68000000000001</v>
+      </c>
+      <c r="G92">
+        <v>11.5</v>
+      </c>
+      <c r="H92">
+        <v>44.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.76</v>
+      </c>
+      <c r="K92">
+        <v>0.035</v>
+      </c>
+      <c r="L92">
+        <v>3.725</v>
+      </c>
+      <c r="M92">
+        <v>14.012784</v>
+      </c>
+      <c r="N92">
+        <v>-10.287784</v>
+      </c>
+      <c r="O92">
+        <v>-2.571946000000001</v>
+      </c>
+      <c r="P92">
+        <v>-7.715838000000002</v>
+      </c>
+      <c r="Q92">
+        <v>-7.680838000000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.681921954823222</v>
+      </c>
+      <c r="T92">
+        <v>6.990043713700603</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06645717225071048</v>
+      </c>
+      <c r="W92">
+        <v>0.2229300272665304</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.265828689002842</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2708292200221995</v>
+      </c>
+      <c r="C93">
+        <v>-31.58822345055261</v>
+      </c>
+      <c r="D93">
+        <v>16.24377654944739</v>
+      </c>
+      <c r="E93">
+        <v>38.83200000000001</v>
+      </c>
+      <c r="F93">
+        <v>59.33200000000001</v>
+      </c>
+      <c r="G93">
+        <v>11.5</v>
+      </c>
+      <c r="H93">
+        <v>44.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.76</v>
+      </c>
+      <c r="K93">
+        <v>0.035</v>
+      </c>
+      <c r="L93">
+        <v>3.725</v>
+      </c>
+      <c r="M93">
+        <v>14.1684816</v>
+      </c>
+      <c r="N93">
+        <v>-10.4434816</v>
+      </c>
+      <c r="O93">
+        <v>-2.610870400000001</v>
+      </c>
+      <c r="P93">
+        <v>-7.832611200000002</v>
+      </c>
+      <c r="Q93">
+        <v>-7.797611200000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.75337994980358</v>
+      </c>
+      <c r="T93">
+        <v>7.766715237445114</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06572687365454882</v>
+      </c>
+      <c r="W93">
+        <v>0.2231044225712937</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2629074946181953</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2728292200221995</v>
+      </c>
+      <c r="C94">
+        <v>-32.37904181304518</v>
+      </c>
+      <c r="D94">
+        <v>16.10495818695482</v>
+      </c>
+      <c r="E94">
+        <v>39.484</v>
+      </c>
+      <c r="F94">
+        <v>59.984</v>
+      </c>
+      <c r="G94">
+        <v>11.5</v>
+      </c>
+      <c r="H94">
+        <v>44.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.76</v>
+      </c>
+      <c r="K94">
+        <v>0.035</v>
+      </c>
+      <c r="L94">
+        <v>3.725</v>
+      </c>
+      <c r="M94">
+        <v>14.3241792</v>
+      </c>
+      <c r="N94">
+        <v>-10.5991792</v>
+      </c>
+      <c r="O94">
+        <v>-2.6497948</v>
+      </c>
+      <c r="P94">
+        <v>-7.949384400000001</v>
+      </c>
+      <c r="Q94">
+        <v>-7.914384400000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8427024435290278</v>
+      </c>
+      <c r="T94">
+        <v>8.737554642125756</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06501245111482547</v>
+      </c>
+      <c r="W94">
+        <v>0.2232750266737797</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2600498044593019</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2748292200221995</v>
+      </c>
+      <c r="C95">
+        <v>-33.16750761321552</v>
+      </c>
+      <c r="D95">
+        <v>15.96849238678449</v>
+      </c>
+      <c r="E95">
+        <v>40.136</v>
+      </c>
+      <c r="F95">
+        <v>60.636</v>
+      </c>
+      <c r="G95">
+        <v>11.5</v>
+      </c>
+      <c r="H95">
+        <v>44.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.76</v>
+      </c>
+      <c r="K95">
+        <v>0.035</v>
+      </c>
+      <c r="L95">
+        <v>3.725</v>
+      </c>
+      <c r="M95">
+        <v>14.4798768</v>
+      </c>
+      <c r="N95">
+        <v>-10.7548768</v>
+      </c>
+      <c r="O95">
+        <v>-2.6887192</v>
+      </c>
+      <c r="P95">
+        <v>-8.0661576</v>
+      </c>
+      <c r="Q95">
+        <v>-8.0311576</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9575456497474604</v>
+      </c>
+      <c r="T95">
+        <v>9.985776733858007</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06431339250068756</v>
+      </c>
+      <c r="W95">
+        <v>0.2234419618708358</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2572535700027503</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2768292200221995</v>
+      </c>
+      <c r="C96">
+        <v>-33.95368015207688</v>
+      </c>
+      <c r="D96">
+        <v>15.83431984792313</v>
+      </c>
+      <c r="E96">
+        <v>40.788</v>
+      </c>
+      <c r="F96">
+        <v>61.288</v>
+      </c>
+      <c r="G96">
+        <v>11.5</v>
+      </c>
+      <c r="H96">
+        <v>44.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.76</v>
+      </c>
+      <c r="K96">
+        <v>0.035</v>
+      </c>
+      <c r="L96">
+        <v>3.725</v>
+      </c>
+      <c r="M96">
+        <v>14.6355744</v>
+      </c>
+      <c r="N96">
+        <v>-10.9105744</v>
+      </c>
+      <c r="O96">
+        <v>-2.7276436</v>
+      </c>
+      <c r="P96">
+        <v>-8.182930800000001</v>
+      </c>
+      <c r="Q96">
+        <v>-8.147930800000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.110669924705371</v>
+      </c>
+      <c r="T96">
+        <v>11.65007285616768</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0636292074740845</v>
+      </c>
+      <c r="W96">
+        <v>0.2236053452551886</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2545168298963381</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2788292200221995</v>
+      </c>
+      <c r="C97">
+        <v>-34.73761675418273</v>
+      </c>
+      <c r="D97">
+        <v>15.70238324581728</v>
+      </c>
+      <c r="E97">
+        <v>41.44</v>
+      </c>
+      <c r="F97">
+        <v>61.94</v>
+      </c>
+      <c r="G97">
+        <v>11.5</v>
+      </c>
+      <c r="H97">
+        <v>44.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.76</v>
+      </c>
+      <c r="K97">
+        <v>0.035</v>
+      </c>
+      <c r="L97">
+        <v>3.725</v>
+      </c>
+      <c r="M97">
+        <v>14.791272</v>
+      </c>
+      <c r="N97">
+        <v>-11.066272</v>
+      </c>
+      <c r="O97">
+        <v>-2.766568</v>
+      </c>
+      <c r="P97">
+        <v>-8.299704000000002</v>
+      </c>
+      <c r="Q97">
+        <v>-8.264704000000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.325043909646445</v>
+      </c>
+      <c r="T97">
+        <v>13.98008742740122</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06295942634277835</v>
+      </c>
+      <c r="W97">
+        <v>0.2237652889893445</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2518377053711134</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2808292200221995</v>
+      </c>
+      <c r="C98">
+        <v>-35.51937284928873</v>
+      </c>
+      <c r="D98">
+        <v>15.57262715071127</v>
+      </c>
+      <c r="E98">
+        <v>42.092</v>
+      </c>
+      <c r="F98">
+        <v>62.592</v>
+      </c>
+      <c r="G98">
+        <v>11.5</v>
+      </c>
+      <c r="H98">
+        <v>44.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.76</v>
+      </c>
+      <c r="K98">
+        <v>0.035</v>
+      </c>
+      <c r="L98">
+        <v>3.725</v>
+      </c>
+      <c r="M98">
+        <v>14.9469696</v>
+      </c>
+      <c r="N98">
+        <v>-11.2219696</v>
+      </c>
+      <c r="O98">
+        <v>-2.8054924</v>
+      </c>
+      <c r="P98">
+        <v>-8.416477200000001</v>
+      </c>
+      <c r="Q98">
+        <v>-8.381477200000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.646604887058053</v>
+      </c>
+      <c r="T98">
+        <v>17.47510928425148</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06230359898504108</v>
+      </c>
+      <c r="W98">
+        <v>0.2239219005623722</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2492143959401644</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2828292200221995</v>
+      </c>
+      <c r="C99">
+        <v>-36.29900204999916</v>
+      </c>
+      <c r="D99">
+        <v>15.44499795000084</v>
+      </c>
+      <c r="E99">
+        <v>42.744</v>
+      </c>
+      <c r="F99">
+        <v>63.244</v>
+      </c>
+      <c r="G99">
+        <v>11.5</v>
+      </c>
+      <c r="H99">
+        <v>44.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.76</v>
+      </c>
+      <c r="K99">
+        <v>0.035</v>
+      </c>
+      <c r="L99">
+        <v>3.725</v>
+      </c>
+      <c r="M99">
+        <v>15.1026672</v>
+      </c>
+      <c r="N99">
+        <v>-11.3776672</v>
+      </c>
+      <c r="O99">
+        <v>-2.8444168</v>
+      </c>
+      <c r="P99">
+        <v>-8.5332504</v>
+      </c>
+      <c r="Q99">
+        <v>-8.4982504</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.182539849410738</v>
+      </c>
+      <c r="T99">
+        <v>23.30014571233532</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0616612938408654</v>
+      </c>
+      <c r="W99">
+        <v>0.2240752830308013</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2466451753634616</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2848292200221995</v>
+      </c>
+      <c r="C100">
+        <v>-37.07655622562601</v>
+      </c>
+      <c r="D100">
+        <v>15.31944377437399</v>
+      </c>
+      <c r="E100">
+        <v>43.396</v>
+      </c>
+      <c r="F100">
+        <v>63.896</v>
+      </c>
+      <c r="G100">
+        <v>11.5</v>
+      </c>
+      <c r="H100">
+        <v>44.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.76</v>
+      </c>
+      <c r="K100">
+        <v>0.035</v>
+      </c>
+      <c r="L100">
+        <v>3.725</v>
+      </c>
+      <c r="M100">
+        <v>15.2583648</v>
+      </c>
+      <c r="N100">
+        <v>-11.5333648</v>
+      </c>
+      <c r="O100">
+        <v>-2.8833412</v>
+      </c>
+      <c r="P100">
+        <v>-8.650023600000001</v>
+      </c>
+      <c r="Q100">
+        <v>-8.615023600000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.254409774116107</v>
+      </c>
+      <c r="T100">
+        <v>34.95021856850298</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0610320969649382</v>
+      </c>
+      <c r="W100">
+        <v>0.2242255352447728</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2441283878597528</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2868292200221995</v>
+      </c>
+      <c r="C101">
+        <v>-37.85208557247476</v>
+      </c>
+      <c r="D101">
+        <v>15.19591442752524</v>
+      </c>
+      <c r="E101">
+        <v>44.048</v>
+      </c>
+      <c r="F101">
+        <v>64.548</v>
+      </c>
+      <c r="G101">
+        <v>11.5</v>
+      </c>
+      <c r="H101">
+        <v>44.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.76</v>
+      </c>
+      <c r="K101">
+        <v>0.035</v>
+      </c>
+      <c r="L101">
+        <v>3.725</v>
+      </c>
+      <c r="M101">
+        <v>15.4140624</v>
+      </c>
+      <c r="N101">
+        <v>-11.6890624</v>
+      </c>
+      <c r="O101">
+        <v>-2.9222656</v>
+      </c>
+      <c r="P101">
+        <v>-8.766796800000002</v>
+      </c>
+      <c r="Q101">
+        <v>-8.731796800000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.470019548232214</v>
+      </c>
+      <c r="T101">
+        <v>69.90043713700595</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06041561113700953</v>
+      </c>
+      <c r="W101">
+        <v>0.2243727520604821</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2416624445480381</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
